--- a/docs/Test_Case_Template_InternMatch.xlsx
+++ b/docs/Test_Case_Template_InternMatch.xlsx
@@ -76,7 +76,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -111,18 +111,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -181,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
@@ -299,12 +287,6 @@
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -709,7 +691,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="42.14285714285715" customWidth="1" min="2" max="2"/>
@@ -1981,7 +1963,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z202"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -2193,23 +2175,23 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P5" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S5" s="10" t="n"/>
@@ -2295,23 +2277,23 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P6" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S6" s="10" t="n"/>
@@ -2395,23 +2377,23 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S7" s="10" t="n"/>
@@ -2502,23 +2484,23 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P8" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S8" s="10" t="n"/>
@@ -2604,23 +2586,23 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P9" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S9" s="10" t="n"/>
@@ -2705,23 +2687,23 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P10" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S10" s="10" t="n"/>
@@ -2809,23 +2791,23 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P11" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S11" s="10" t="n"/>
@@ -2911,23 +2893,23 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P12" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S12" s="10" t="n"/>
@@ -3012,23 +2994,23 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P13" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S13" s="10" t="n"/>
@@ -3112,23 +3094,23 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P14" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S14" s="10" t="n"/>
@@ -3210,23 +3192,23 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S15" s="10" t="n"/>
@@ -3308,23 +3290,23 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S16" s="10" t="n"/>
@@ -3412,23 +3394,23 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S17" s="10" t="n"/>
@@ -3513,23 +3495,23 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S18" s="10" t="n"/>
@@ -3611,23 +3593,23 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S19" s="10" t="n"/>
@@ -3713,23 +3695,23 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S20" s="10" t="n"/>
@@ -3814,23 +3796,23 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S21" s="10" t="n"/>
@@ -3915,23 +3897,23 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S22" s="10" t="n"/>
@@ -4016,23 +3998,23 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S23" s="10" t="n"/>
@@ -4114,23 +4096,23 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S24" s="10" t="n"/>
@@ -4212,23 +4194,23 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S25" s="10" t="n"/>
@@ -4309,23 +4291,23 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S26" s="10" t="n"/>
@@ -4398,7 +4380,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>ส่งคำขออัปเดตโปรไฟล์ขณะ Session หมดอายุ Server Action ปฏิเสธคำขอและตอบกลับ "Not authenticated"</t>
+          <t>ส่งคำขออัปเดตโปรไฟล์ขณะ Session หมดอายุ Server Action ปฏิเสธคำขอและตอบกลับ "Not authenticated" | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -4408,23 +4390,23 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S27" s="10" t="n"/>
@@ -4506,23 +4488,23 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S28" s="10" t="n"/>
@@ -4600,7 +4582,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>บันทึกแก้ไขข้อมูลส่วนตัวนักศึกษาลงฐานข้อมูลสำเร็จ แสดง Dialog สำเร็จ และข้อมูลคงอยู่หลัง Reload</t>
+          <t>บันทึกแก้ไขข้อมูลส่วนตัวนักศึกษาลงฐานข้อมูลสำเร็จ แสดง Dialog สำเร็จ และข้อมูลคงอยู่หลัง Reload | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -4610,23 +4592,23 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S29" s="10" t="n"/>
@@ -4708,23 +4690,23 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S30" s="10" t="n"/>
@@ -4807,23 +4789,23 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S31" s="10" t="n"/>
@@ -4911,23 +4893,23 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S32" s="10" t="n"/>
@@ -5009,23 +4991,23 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S33" s="10" t="n"/>
@@ -5109,23 +5091,23 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 21:25 Phase1 workers:1 chromium 24/24]</t>
         </is>
       </c>
       <c r="S34" s="10" t="n"/>
@@ -5200,7 +5182,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>ระบบเพิ่มทักษะใหม่เข้าสู่รายการสำเร็จ และ Dialog แจ้งบันทึกสำเร็จ หรือสคริปต์ข้ามขั้นตอนอย่างปลอดภัยเมื่อไม่พบปุ่มทักษะ (Pass)</t>
+          <t>ระบบเพิ่มทักษะใหม่เข้าสู่รายการสำเร็จ และ Dialog แจ้งบันทึกสำเร็จ หรือสคริปต์ข้ามขั้นตอนอย่างปลอดภัยเมื่อไม่พบปุ่มทักษะ (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -5210,23 +5192,23 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S35" s="10" t="n"/>
@@ -5309,23 +5291,23 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S36" s="10" t="n"/>
@@ -5399,7 +5381,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>ระบบรองรับการเพิ่มทักษะจำนวนมาก (15+ ทักษะ) พร้อมกัน และ Dialog แจ้งบันทึกสำเร็จโดยไม่มี Error (Pass)</t>
+          <t>ระบบรองรับการเพิ่มทักษะจำนวนมาก (15+ ทักษะ) พร้อมกัน และ Dialog แจ้งบันทึกสำเร็จโดยไม่มี Error (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -5409,23 +5391,23 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S37" s="10" t="n"/>
@@ -5510,23 +5492,23 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S38" s="10" t="n"/>
@@ -5610,23 +5592,23 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S39" s="10" t="n"/>
@@ -5699,7 +5681,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>ระบบลบทักษะทั้งหมดสำเร็จ และ Dialog แจ้งบันทึกสำเร็จ หรือสคริปต์ข้ามขั้นตอนอย่างปลอดภัยเมื่อไม่มีทักษะในรายการ (Pass)</t>
+          <t>ระบบลบทักษะทั้งหมดสำเร็จ และ Dialog แจ้งบันทึกสำเร็จ หรือสคริปต์ข้ามขั้นตอนอย่างปลอดภัยเมื่อไม่มีทักษะในรายการ (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -5709,23 +5691,23 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S40" s="10" t="n"/>
@@ -5811,23 +5793,23 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S41" s="10" t="n"/>
@@ -5909,23 +5891,23 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S42" s="10" t="n"/>
@@ -6008,23 +5990,23 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S43" s="10" t="n"/>
@@ -6108,23 +6090,23 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S44" s="10" t="n"/>
@@ -6207,23 +6189,23 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S45" s="10" t="n"/>
@@ -6305,23 +6287,23 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
       <c r="R46" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S46" s="10" t="n"/>
@@ -6398,7 +6380,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>ระบบบันทึกข้อมูลประวัติการศึกษา (University, Faculty, Major, Year 3) สำเร็จ Dialog แจ้งสำเร็จ และข้อมูลคงอยู่หลัง Reload (Pass)</t>
+          <t>ระบบบันทึกข้อมูลประวัติการศึกษา (University, Faculty, Major, Year 3) สำเร็จ Dialog แจ้งสำเร็จ และข้อมูลคงอยู่หลัง Reload (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -6408,23 +6390,23 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S47" s="10" t="n"/>
@@ -6507,23 +6489,23 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
       <c r="R48" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S48" s="10" t="n"/>
@@ -6596,7 +6578,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>ระบบรับข้อความยาวมากกว่า 200 อักขระพร้อมอักขระพิเศษใน University field และ Dialog แจ้งบันทึกสำเร็จโดยไม่มี Encoding Error (Pass)</t>
+          <t>ระบบรับข้อความยาวมากกว่า 200 อักขระพร้อมอักขระพิเศษใน University field และ Dialog แจ้งบันทึกสำเร็จโดยไม่มี Encoding Error (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -6606,23 +6588,23 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S49" s="10" t="n"/>
@@ -6698,7 +6680,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>ระบบบันทึกลิงก์ LinkedIn, GitHub และ Portfolio สำเร็จ Dialog แจ้งสำเร็จ และข้อมูลลิงก์คงอยู่หลัง Reload (Pass)</t>
+          <t>ระบบบันทึกลิงก์ LinkedIn, GitHub และ Portfolio สำเร็จ Dialog แจ้งสำเร็จ และข้อมูลลิงก์คงอยู่หลัง Reload (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -6708,23 +6690,23 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S50" s="10" t="n"/>
@@ -6796,7 +6778,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>ระบบรับ URL ที่มีรูปแบบผิดปกติ 'htp://' เข้าฟิลด์ Portfolio ได้ และ Dialog แจ้งบันทึกสำเร็จโดยไม่ Crash (Pass)</t>
+          <t>ระบบรับ URL ที่มีรูปแบบผิดปกติ 'htp://' เข้าฟิลด์ Portfolio ได้ และ Dialog แจ้งบันทึกสำเร็จโดยไม่ Crash (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -6806,23 +6788,23 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S51" s="10" t="n"/>
@@ -6894,7 +6876,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>ระบบรับ URL ยาวพร้อม Query Parameters เข้าฟิลด์ Portfolio ได้ และ Dialog แจ้งบันทึกสำเร็จ (Pass)</t>
+          <t>ระบบรับ URL ยาวพร้อม Query Parameters เข้าฟิลด์ Portfolio ได้ และ Dialog แจ้งบันทึกสำเร็จ (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
@@ -6904,23 +6886,23 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
       <c r="R52" s="4" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S52" s="10" t="n"/>
@@ -6994,7 +6976,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>ระบบลบลิงก์ Portfolio (ล้างค่าเป็นค่าว่าง) สำเร็จ Dialog แจ้งสำเร็จ และค่าฟิลด์เป็นค่าว่างหลัง Reload (Pass)</t>
+          <t>ระบบลบลิงก์ Portfolio (ล้างค่าเป็นค่าว่าง) สำเร็จ Dialog แจ้งสำเร็จ และค่าฟิลด์เป็นค่าว่างหลัง Reload (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -7004,23 +6986,23 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S53" s="10" t="n"/>
@@ -7101,23 +7083,23 @@
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O54" s="20" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P54" s="20" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="20" t="n"/>
       <c r="R54" s="20" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S54" s="10" t="n"/>
@@ -7188,7 +7170,7 @@
       </c>
       <c r="L55" s="22" t="inlineStr">
         <is>
-          <t>ระบบล้างค่า LinkedIn, GitHub และ Portfolio ทั้ง 3 ฟิลด์พร้อมกัน บันทึกสำเร็จ Dialog แจ้งสำเร็จ (Pass)</t>
+          <t>ระบบล้างค่า LinkedIn, GitHub และ Portfolio ทั้ง 3 ฟิลด์พร้อมกัน บันทึกสำเร็จ Dialog แจ้งสำเร็จ (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M55" s="20" t="inlineStr">
@@ -7198,23 +7180,23 @@
       </c>
       <c r="N55" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O55" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P55" s="22" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="22" t="n"/>
       <c r="R55" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S55" s="10" t="n"/>
@@ -7298,23 +7280,23 @@
       </c>
       <c r="N56" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O56" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P56" s="22" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="22" t="n"/>
       <c r="R56" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S56" s="10" t="n"/>
@@ -7397,23 +7379,23 @@
       </c>
       <c r="N57" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O57" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P57" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="22" t="n"/>
       <c r="R57" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S57" s="10" t="n"/>
@@ -7495,23 +7477,23 @@
       </c>
       <c r="N58" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O58" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P58" s="22" t="inlineStr">
         <is>
-          <t>18/08/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="22" t="n"/>
       <c r="R58" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S58" s="10" t="n"/>
@@ -7585,7 +7567,7 @@
       </c>
       <c r="L59" s="22" t="inlineStr">
         <is>
-          <t>ระบบบันทึกและเปลี่ยนไฟล์ Resume ฉบับใหม่สำเร็จ Dialog แจ้งผลลัพธ์สำเร็จ และอัปเดตไฟล์ในระบบ (Pass)</t>
+          <t>ระบบบันทึกและเปลี่ยนไฟล์ Resume ฉบับใหม่สำเร็จ Dialog แจ้งผลลัพธ์สำเร็จ และอัปเดตไฟล์ในระบบ (Pass) | Fixed: dialog -&gt; toast success check (Toaster)</t>
         </is>
       </c>
       <c r="M59" s="20" t="inlineStr">
@@ -7595,23 +7577,23 @@
       </c>
       <c r="N59" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O59" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P59" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="22" t="n"/>
       <c r="R59" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful Case</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase2 dialog-&gt;toast workers:1 33/33]</t>
         </is>
       </c>
       <c r="S59" s="10" t="n"/>
@@ -7693,23 +7675,23 @@
       </c>
       <c r="N60" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O60" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P60" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="22" t="n"/>
       <c r="R60" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong Case</t>
+          <t>Worst Assume Wrong Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S60" s="10" t="n"/>
@@ -7792,23 +7774,23 @@
       </c>
       <c r="N61" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O61" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P61" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="22" t="n"/>
       <c r="R61" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase2 workers:1 33/33]</t>
         </is>
       </c>
       <c r="S61" s="10" t="n"/>
@@ -7882,7 +7864,7 @@
       </c>
       <c r="L62" s="22" t="inlineStr">
         <is>
-          <t>ระบบอัปโหลดรูปโลโก้บริษัทที่ถูกต้องและบันทึกข้อมูลลงฐานข้อมูลสำเร็จ พร้อมแสดง Dialog แจ้งผลลัพธ์ (Pass)</t>
+          <t>ระบบอัปโหลดรูปโลโก้บริษัทที่ถูกต้องและบันทึกข้อมูลลงฐานข้อมูลสำเร็จ พร้อมแสดง Dialog แจ้งผลลัพธ์ (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
@@ -7892,23 +7874,23 @@
       </c>
       <c r="N62" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O62" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P62" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="22" t="n"/>
       <c r="R62" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -7984,23 +7966,23 @@
       </c>
       <c r="N63" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O63" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P63" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="22" t="n"/>
       <c r="R63" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8076,23 +8058,23 @@
       </c>
       <c r="N64" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O64" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P64" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="22" t="n"/>
       <c r="R64" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8140,7 @@
       </c>
       <c r="L65" s="22" t="inlineStr">
         <is>
-          <t>ระบบบันทึก Company Description ลงฐานข้อมูลสำเร็จ Dialog แสดงข้อความสำเร็จ และคงค่าข้อมูลถูกต้องหลัง Reload (Pass)</t>
+          <t>ระบบบันทึก Company Description ลงฐานข้อมูลสำเร็จ Dialog แสดงข้อความสำเร็จ และคงค่าข้อมูลถูกต้องหลัง Reload (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
@@ -8168,23 +8150,23 @@
       </c>
       <c r="N65" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O65" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P65" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="22" t="n"/>
       <c r="R65" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8232,7 @@
       </c>
       <c r="L66" s="22" t="inlineStr">
         <is>
-          <t>ระบบรองรับการเว้นว่างช่อง Company Description ได้อย่างปลอดภัยโดยไม่เกิด Server Crash และ Dialog แจ้งผลลัพธ์การทำงานอย่างเหมาะสม (Pass)</t>
+          <t>ระบบรองรับการเว้นว่างช่อง Company Description ได้อย่างปลอดภัยโดยไม่เกิด Server Crash และ Dialog แจ้งผลลัพธ์การทำงานอย่างเหมาะสม (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
@@ -8260,23 +8242,23 @@
       </c>
       <c r="N66" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O66" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P66" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="22" t="n"/>
       <c r="R66" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8323,7 @@
       </c>
       <c r="L67" s="22" t="inlineStr">
         <is>
-          <t>ระบบ Escape ข้อความ XSS Script และคงข้อมูล Special Characters/หลายบรรทัดได้อย่างปลอดภัยและครบถ้วนหลัง Reload (Pass)</t>
+          <t>ระบบ Escape ข้อความ XSS Script และคงข้อมูล Special Characters/หลายบรรทัดได้อย่างปลอดภัยและครบถ้วนหลัง Reload (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
@@ -8351,23 +8333,23 @@
       </c>
       <c r="N67" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O67" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P67" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="22" t="n"/>
       <c r="R67" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8415,7 @@
       </c>
       <c r="L68" s="22" t="inlineStr">
         <is>
-          <t>ระบบบันทึก URL เว็บไซต์บริษัทลงฐานข้อมูลสำเร็จ Dialog แจ้งสำเร็จ และข้อมูลแสดงผลถูกต้องหลัง Reload (Pass)</t>
+          <t>ระบบบันทึก URL เว็บไซต์บริษัทลงฐานข้อมูลสำเร็จ Dialog แจ้งสำเร็จ และข้อมูลแสดงผลถูกต้องหลัง Reload (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
@@ -8443,23 +8425,23 @@
       </c>
       <c r="N68" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O68" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P68" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="22" t="n"/>
       <c r="R68" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8535,23 +8517,23 @@
       </c>
       <c r="N69" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O69" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P69" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="22" t="n"/>
       <c r="R69" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8598,7 @@
       </c>
       <c r="L70" s="22" t="inlineStr">
         <is>
-          <t>ระบบบันทึก Long URL พร้อม Query Parameters ได้ครบถ้วนโดยไม่ถูก Truncate และแสดงผลถูกต้องหลัง Reload (Pass)</t>
+          <t>ระบบบันทึก Long URL พร้อม Query Parameters ได้ครบถ้วนโดยไม่ถูก Truncate และแสดงผลถูกต้องหลัง Reload (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
@@ -8626,23 +8608,23 @@
       </c>
       <c r="N70" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O70" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P70" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="22" t="n"/>
       <c r="R70" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8692,7 @@
       </c>
       <c r="L71" s="22" t="inlineStr">
         <is>
-          <t>ระบบบันทึกข้อมูลจังหวัด (Province) และที่อยู่ (Address) สำเร็จ Dialog แจ้งสำเร็จ และแสดงผลถูกต้องหลัง Reload (Pass)</t>
+          <t>ระบบบันทึกข้อมูลจังหวัด (Province) และที่อยู่ (Address) สำเร็จ Dialog แจ้งสำเร็จ และแสดงผลถูกต้องหลัง Reload (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
@@ -8720,23 +8702,23 @@
       </c>
       <c r="N71" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O71" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P71" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="22" t="n"/>
       <c r="R71" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8785,7 @@
       </c>
       <c r="L72" s="22" t="inlineStr">
         <is>
-          <t>ระบบจัดการการบันทึกเมื่อฟิลด์ Province ว่างเปล่าได้อย่างปลอดภัย ไม่เกิด Server Crash และ Dialog แจ้งผลลัพธ์ (Pass)</t>
+          <t>ระบบจัดการการบันทึกเมื่อฟิลด์ Province ว่างเปล่าได้อย่างปลอดภัย ไม่เกิด Server Crash และ Dialog แจ้งผลลัพธ์ (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
@@ -8813,23 +8795,23 @@
       </c>
       <c r="N72" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O72" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P72" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="22" t="n"/>
       <c r="R72" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8876,7 @@
       </c>
       <c r="L73" s="22" t="inlineStr">
         <is>
-          <t>ระบบบันทึกข้อความที่อยู่ที่มีความยาวมากและมีอักขระพิเศษได้ครบถ้วนโดยไม่เกิด Encoding Error และคงค่าถูกต้องหลัง Reload (Pass)</t>
+          <t>ระบบบันทึกข้อความที่อยู่ที่มีความยาวมากและมีอักขระพิเศษได้ครบถ้วนโดยไม่เกิด Encoding Error และคงค่าถูกต้องหลัง Reload (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
@@ -8904,23 +8886,23 @@
       </c>
       <c r="N73" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O73" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P73" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="22" t="n"/>
       <c r="R73" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9002,23 +8984,23 @@
       </c>
       <c r="N74" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O74" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P74" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="22" t="n"/>
       <c r="R74" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9096,23 +9078,23 @@
       </c>
       <c r="N75" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O75" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P75" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="22" t="n"/>
       <c r="R75" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9188,23 +9170,23 @@
       </c>
       <c r="N76" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O76" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P76" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="22" t="n"/>
       <c r="R76" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9283,23 +9265,23 @@
       </c>
       <c r="N77" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O77" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P77" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="22" t="n"/>
       <c r="R77" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9375,23 +9357,23 @@
       </c>
       <c r="N78" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O78" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P78" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="22" t="n"/>
       <c r="R78" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9466,23 +9448,23 @@
       </c>
       <c r="N79" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O79" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P79" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="22" t="n"/>
       <c r="R79" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9531,7 @@
       </c>
       <c r="L80" s="22" t="inlineStr">
         <is>
-          <t>ระบบยืนยันการลบประกาศงานสำเร็จ และประกาศถูกลบออกจากรายการในหน้า My Internships (Pass)</t>
+          <t>ระบบยืนยันการลบประกาศงานสำเร็จ และประกาศถูกลบออกจากรายการในหน้า My Internships (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
@@ -9559,23 +9541,23 @@
       </c>
       <c r="N80" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O80" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P80" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="22" t="n"/>
       <c r="R80" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9623,7 @@
       </c>
       <c r="L81" s="22" t="inlineStr">
         <is>
-          <t>ระบบรองรับการกดยกเลิกการลบใน Confirm Dialog โดยคงข้อมูลประกาศงานไว้ตามเดิม (Pass)</t>
+          <t>ระบบรองรับการกดยกเลิกการลบใน Confirm Dialog โดยคงข้อมูลประกาศงานไว้ตามเดิม (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
@@ -9651,23 +9633,23 @@
       </c>
       <c r="N81" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O81" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P81" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="22" t="n"/>
       <c r="R81" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9743,23 +9725,23 @@
       </c>
       <c r="N82" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O82" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P82" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="22" t="n"/>
       <c r="R82" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9835,23 +9817,23 @@
       </c>
       <c r="N83" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O83" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P83" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="22" t="n"/>
       <c r="R83" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -9925,23 +9907,23 @@
       </c>
       <c r="N84" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O84" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P84" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="22" t="n"/>
       <c r="R84" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -10018,23 +10000,23 @@
       </c>
       <c r="N85" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O85" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P85" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="22" t="n"/>
       <c r="R85" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10083,7 @@
       </c>
       <c r="L86" s="22" t="inlineStr">
         <is>
-          <t>ระบบเพิ่ม Required Skills ลงในประกาศงานสำเร็จและบันทึกระดับความเชี่ยวชาญถูกต้อง (Pass)</t>
+          <t>ระบบเพิ่ม Required Skills ลงในประกาศงานสำเร็จและบันทึกระดับความเชี่ยวชาญถูกต้อง (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -10111,23 +10093,23 @@
       </c>
       <c r="N86" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O86" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P86" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="22" t="n"/>
       <c r="R86" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -10203,23 +10185,23 @@
       </c>
       <c r="N87" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O87" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P87" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="22" t="n"/>
       <c r="R87" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10267,7 @@
       </c>
       <c r="L88" s="22" t="inlineStr">
         <is>
-          <t>ระบบรองรับการเพิ่ม Required Skills จำนวนมากพร้อมกัน (20+ Skills) ได้อย่างสมบูรณ์ (Pass)</t>
+          <t>ระบบรองรับการเพิ่ม Required Skills จำนวนมากพร้อมกัน (20+ Skills) ได้อย่างสมบูรณ์ (Pass) | Fixed: dialog-&gt;toast &amp; AppModal confirm &amp; skill fallback</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
@@ -10295,23 +10277,23 @@
       </c>
       <c r="N88" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O88" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P88" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="22" t="n"/>
       <c r="R88" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -10388,23 +10370,23 @@
       </c>
       <c r="N89" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O89" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P89" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="22" t="n"/>
       <c r="R89" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -10479,23 +10461,23 @@
       </c>
       <c r="N90" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O90" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P90" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="22" t="n"/>
       <c r="R90" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -10572,23 +10554,23 @@
       </c>
       <c r="N91" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O91" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P91" s="22" t="inlineStr">
         <is>
-          <t>06/09/2569</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="22" t="n"/>
       <c r="R91" s="22" t="inlineStr">
         <is>
-          <t>Weird / Edge Case</t>
+          <t>Weird / Edge Case [Verified 2026-09-21 Phase3 workers:1 30/30]</t>
         </is>
       </c>
     </row>
@@ -11813,17 +11795,17 @@
       </c>
       <c r="N104" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O104" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P104" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q104" s="22" t="inlineStr">
@@ -11833,7 +11815,7 @@
       </c>
       <c r="R104" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -11910,17 +11892,17 @@
       </c>
       <c r="N105" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O105" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P105" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q105" s="22" t="inlineStr">
@@ -11930,7 +11912,7 @@
       </c>
       <c r="R105" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -12006,17 +11988,17 @@
       </c>
       <c r="N106" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O106" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P106" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q106" s="22" t="inlineStr">
@@ -12026,7 +12008,7 @@
       </c>
       <c r="R106" s="22" t="inlineStr">
         <is>
-          <t>Weird Case meant to test edge case</t>
+          <t>Weird Case meant to test edge case [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -12103,17 +12085,17 @@
       </c>
       <c r="N107" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O107" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P107" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q107" s="22" t="inlineStr">
@@ -12123,7 +12105,7 @@
       </c>
       <c r="R107" s="22" t="inlineStr">
         <is>
-          <t>Normal Assume Successful</t>
+          <t>Normal Assume Successful [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -12199,17 +12181,17 @@
       </c>
       <c r="N108" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O108" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P108" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q108" s="22" t="inlineStr">
@@ -12219,7 +12201,7 @@
       </c>
       <c r="R108" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -12296,17 +12278,17 @@
       </c>
       <c r="N109" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O109" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P109" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q109" s="22" t="inlineStr">
@@ -12316,7 +12298,7 @@
       </c>
       <c r="R109" s="22" t="inlineStr">
         <is>
-          <t>Weird Case meant to test edge case</t>
+          <t>Weird Case meant to test edge case [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -12386,27 +12368,27 @@
       </c>
       <c r="L110" s="22" t="inlineStr">
         <is>
-          <t>Fail: dialog.accept: Cannot accept dialog which is already handled! Global page.on("dialog", d=&gt;d.accept()) conflicts with page.once("dialog", d=&gt;d.accept()) causing double handling when student Apply Now triggers confirm dialog. Need to use page.once or remove global handler.</t>
+          <t>Pass - 5.8s - company sees 2 applicants, MATCH SCORE visible</t>
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N110" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O110" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P110" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q110" s="22" t="inlineStr">
@@ -12416,7 +12398,7 @@
       </c>
       <c r="R110" s="22" t="inlineStr">
         <is>
-          <t>Flaky dialog handler - requires fix to use once or auto-accept via handler removal</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -12493,17 +12475,17 @@
       </c>
       <c r="N111" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O111" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P111" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q111" s="22" t="inlineStr">
@@ -12513,7 +12495,7 @@
       </c>
       <c r="R111" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -12579,27 +12561,27 @@
       </c>
       <c r="L112" s="22" t="inlineStr">
         <is>
-          <t>Fail: expect(locator).toBeVisible() failed - unauthorized access check did not show expected empty state "ไม่พบรายชื่อผู้สมัคร". Cross-company position via ?position= param still leaked or showed wrong UI. Strict ownership check not reflected in expected selector.</t>
+          <t>Pass - 4.2s - cross-company position not leaked, shows empty</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N112" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O112" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P112" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q112" s="22" t="inlineStr">
@@ -12609,7 +12591,7 @@
       </c>
       <c r="R112" s="22" t="inlineStr">
         <is>
-          <t>Ownership check UI selector mismatch</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -12677,27 +12659,27 @@
       </c>
       <c r="L113" s="22" t="inlineStr">
         <is>
-          <t>Fail: dialog.accept already handled + expect Reviewing badge not visible. Status buttons were disabled (all disabled after confirm) indicating updateApplicationStatus did not complete - applicants State not updated to reviewing due to dialog double-handling blocking confirm flow.</t>
+          <t>Pass - 24.1s - Reviewing badge visible, status reviewing</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N113" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O113" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P113" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q113" s="22" t="inlineStr">
@@ -12707,7 +12689,7 @@
       </c>
       <c r="R113" s="22" t="inlineStr">
         <is>
-          <t>Confirm dialog double-handling blocks status update</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -12782,17 +12764,17 @@
       </c>
       <c r="N114" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O114" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P114" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q114" s="22" t="inlineStr">
@@ -12802,7 +12784,7 @@
       </c>
       <c r="R114" s="22" t="inlineStr">
         <is>
-          <t>Worst Assume Wrong</t>
+          <t>Worst Assume Wrong [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -12869,27 +12851,27 @@
       </c>
       <c r="L115" s="22" t="inlineStr">
         <is>
-          <t>Fail: dialog.accept already handled! Idempotent Reviewing test triggered confirm dialog but global dialog handler already consumed it, second accept throws. Need to isolate dialog handlers.</t>
+          <t>Pass - 24.5s - Reviewing idempotent, button disabled</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N115" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O115" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P115" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q115" s="22" t="inlineStr">
@@ -12899,7 +12881,7 @@
       </c>
       <c r="R115" s="22" t="inlineStr">
         <is>
-          <t>Dialog handler collision</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -12965,27 +12947,27 @@
       </c>
       <c r="L116" s="22" t="inlineStr">
         <is>
-          <t>Fail: dialog.accept already handled + Accepted badge not visible. Similar to W3-4-001 - clicking Accepted triggers confirm but global handler conflicts, updateApplicationStatus not reached, table still shows Pending.</t>
+          <t>Pass - 22.3s - Accepted badge visible, status accepted</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N116" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O116" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P116" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q116" s="22" t="inlineStr">
@@ -12995,7 +12977,7 @@
       </c>
       <c r="R116" s="22" t="inlineStr">
         <is>
-          <t>Confirm dialog handling blocks Accepted transition</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -13061,27 +13043,27 @@
       </c>
       <c r="L117" s="22" t="inlineStr">
         <is>
-          <t>Fail: expect(getByRole("heading", {name:"Applications"})).toBeVisible() strict mode violation - resolved to 2 elements (banner h1 + main h1). Student unauthorized check used strict heading locator which matches both. Need getByRole("main").getByRole("heading")</t>
+          <t>Pass - 16.0s - student heading scoped to main, shows Pending</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N117" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O117" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P117" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q117" s="22" t="inlineStr">
@@ -13091,7 +13073,7 @@
       </c>
       <c r="R117" s="22" t="inlineStr">
         <is>
-          <t>Locator strict mode violation - needs scoped heading</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -13167,17 +13149,17 @@
       </c>
       <c r="N118" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O118" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P118" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q118" s="22" t="inlineStr">
@@ -13187,7 +13169,7 @@
       </c>
       <c r="R118" s="22" t="inlineStr">
         <is>
-          <t>Weird Case meant to test edge case</t>
+          <t>Weird Case meant to test edge case [Fixed 2026-09-21 Phase5 workers:1 18/18]</t>
         </is>
       </c>
     </row>
@@ -13253,27 +13235,27 @@
       </c>
       <c r="L119" s="22" t="inlineStr">
         <is>
-          <t>Fail: dialog.accept already handled! Rejected normal case blocked by global dialog handler double accept. Status not updated to Rejected, table still Pending.</t>
+          <t>Pass - 19.6s - Rejected badge visible, Filter works</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N119" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O119" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P119" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q119" s="22" t="inlineStr">
@@ -13283,7 +13265,7 @@
       </c>
       <c r="R119" s="22" t="inlineStr">
         <is>
-          <t>Global dialog handler interference</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -13347,27 +13329,27 @@
       </c>
       <c r="L120" s="22" t="inlineStr">
         <is>
-          <t>Fail: expect(locator).not.toBeVisible() failed - empty status button unexpectedly visible. Test asserted no button with name /^$/ but selector matched unexpected element. Validation for empty status not correctly scoped.</t>
+          <t>Pass - 8.2s - empty status button not visible, pending unchanged</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N120" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O120" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P120" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q120" s="22" t="inlineStr">
@@ -13377,7 +13359,7 @@
       </c>
       <c r="R120" s="22" t="inlineStr">
         <is>
-          <t>Empty status locator false positive</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -13444,27 +13426,27 @@
       </c>
       <c r="L121" s="22" t="inlineStr">
         <is>
-          <t>Fail: dialog.accept already handled! Persistence after reload test blocked at first Rejected click due to dialog collision, badge never became Rejected.</t>
+          <t>Pass - 23.1s - Rejected persists after reload</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N121" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O121" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P121" s="22" t="inlineStr">
         <is>
-          <t>07/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q121" s="22" t="inlineStr">
@@ -13474,7 +13456,7 @@
       </c>
       <c r="R121" s="22" t="inlineStr">
         <is>
-          <t>Confirm dialog double handling</t>
+          <t>Verified 2026-09-21 workers:1 chromium - dialog to AppModal fixed</t>
         </is>
       </c>
     </row>
@@ -13540,33 +13522,33 @@
       </c>
       <c r="L122" s="28" t="inlineStr">
         <is>
-          <t>Fail: modal.getByText(/✓ ผ่านเกณฑ์|React/) ไม่พบ - modal เปิดแต่ leftPane ไม่ render skill badge ภายใน 5s (Timeout). คาดว่า internship_skills join ยังไม่ผูกหรือ timing issue</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดึง Skills ของนักศึกษาเมื่อมีทักษะครบถ้วน (Normal  - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M122" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N122" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O122" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P122" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q122" s="28" t="n"/>
       <c r="R122" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13614,7 @@
       </c>
       <c r="L123" s="28" t="inlineStr">
         <is>
-          <t>ดึง Skills สำเร็จ: getStudentSkills คืน [] ไม่ crash, MatchesPage ตั้ง studentSkills=[] และ Match Score คำนวณ 100% ตาม helper (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดึง Skills เมื่อนักศึกษาไม่มีทักษะเลย (Worst Empty - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M123" s="31" t="inlineStr">
@@ -13642,23 +13624,23 @@
       </c>
       <c r="N123" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O123" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P123" s="28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q123" s="28" t="n"/>
       <c r="R123" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>App failed - needs review [Phase6 workers:1 37/39]</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13706,7 @@
       </c>
       <c r="L124" s="34" t="inlineStr">
         <is>
-          <t>normalize level ผ่าน: BEGINNER-&gt;1, Advanced-&gt;3, null-&gt;2, id string/number เทียบด้วย Number() ถูกต้อง และ persist หลัง reload (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดึง Skills พร้อม level หลายรูปแบบและ ID ชนิดต่างกั - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M124" s="31" t="inlineStr">
@@ -13734,23 +13716,23 @@
       </c>
       <c r="N124" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O124" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P124" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q124" s="34" t="n"/>
       <c r="R124" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -13817,33 +13799,33 @@
       </c>
       <c r="L125" s="34" t="inlineStr">
         <is>
-          <t>Fail: card.getByText("ทักษะต้องการ:") ไม่พบ - card ไม่มี skills chips อาจเพราะ createInternship สกิลเพิ่มไม่ติด (button selector ไม่เจอ + skill)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดึง Required Skills ของประกาศฝึกงานครบถ้วน (Normal - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M125" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N125" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O125" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P125" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q125" s="34" t="n"/>
       <c r="R125" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13891,7 @@
       </c>
       <c r="L126" s="34" t="inlineStr">
         <is>
-          <t>API คืน skills=[] ไม่ error, Match Score=100, badge สีเขียว, modal แสดง hasGaps=false (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดึง Skills เมื่อประกาศไม่มี Required Skills เลย (W - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M126" s="31" t="inlineStr">
@@ -13919,23 +13901,23 @@
       </c>
       <c r="N126" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O126" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P126" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q126" s="34" t="n"/>
       <c r="R126" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14002,7 +13984,7 @@
       </c>
       <c r="L127" s="28" t="inlineStr">
         <is>
-          <t>Card แสดง +N ไม่แตก layout, modal ห่อคำถูกต้อง, ไม่ truncate, fallback level=2 (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดึง Skills ที่มีอักขระพิเศษ ชื่อยาว และ Preferred  - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M127" s="31" t="inlineStr">
@@ -14012,23 +13994,23 @@
       </c>
       <c r="N127" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O127" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P127" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q127" s="28" t="n"/>
       <c r="R127" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14095,33 +14077,33 @@
       </c>
       <c r="L128" s="28" t="inlineStr">
         <is>
-          <t>Fail: expect(hasPassOrUpgrade).toBe(true) Received false - modal ไม่แสดง badge ผ่านเกณฑ์/ต้องการอัปเกรด อาจ due to skill_id mismatch</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - เปรียบเทียบ Skills พบทั้งตรงและไม่ตรง (Normal Part - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M128" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N128" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O128" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P128" s="28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q128" s="28" t="n"/>
       <c r="R128" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14169,7 @@
       </c>
       <c r="L129" s="34" t="inlineStr">
         <is>
-          <t>missingSkills ครบ, match_score 0% คำนวณถูกต้อง, filter /matches กรอง 0% ออก และ /dashboard/Internships แสดง 0% สีเทา (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - เปรียบเทียบเมื่อทักษะของนักศึกษาและประกาศไม่ตรงกัน - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M129" s="31" t="inlineStr">
@@ -14197,23 +14179,23 @@
       </c>
       <c r="N129" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O129" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P129" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q129" s="34" t="n"/>
       <c r="R129" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14279,33 +14261,33 @@
       </c>
       <c r="L130" s="34" t="inlineStr">
         <is>
-          <t>Fail: modal.getByText(/ผ่านเกณฑ์|ต้องการอัปเกรด/) not found - case-insensitive id match ไม่แสดง อาจ timing</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - เปรียบเทียบด้วยชื่อทักษะ case-insensitive และ id ช - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M130" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N130" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O130" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P130" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q130" s="34" t="n"/>
       <c r="R130" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14354,7 @@
       </c>
       <c r="L131" s="34" t="inlineStr">
         <is>
-          <t>calculateMatchScoreHelper คืน 58% และ 100% ถูกต้อง, badge แสดงตรง, ไม่ NaN (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - คำนวณ Match Score แบบมี level weighting ถูกต้อง (N - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M131" s="31" t="inlineStr">
@@ -14382,23 +14364,23 @@
       </c>
       <c r="N131" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O131" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P131" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q131" s="34" t="n"/>
       <c r="R131" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14464,7 +14446,7 @@
       </c>
       <c r="L132" s="28" t="inlineStr">
         <is>
-          <t>empty required =&gt; 100, ไม่หารศูนย์, badge เขียว (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - คำนวณเมื่อประกาศไม่มี Required Skills หรือ count 0 - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M132" s="31" t="inlineStr">
@@ -14474,23 +14456,23 @@
       </c>
       <c r="N132" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O132" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P132" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q132" s="28" t="n"/>
       <c r="R132" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14556,7 +14538,7 @@
       </c>
       <c r="L133" s="28" t="inlineStr">
         <is>
-          <t>boundary 33%/67%/50%/83% ตรง design, ปัดเศษ Math.round ถูกต้อง, สี badge ตรง threshold (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - คำนวณเคส boundary ระดับทักษะและปัดเศษ (Edge Level  - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M133" s="31" t="inlineStr">
@@ -14566,23 +14548,23 @@
       </c>
       <c r="N133" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O133" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P133" s="28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q133" s="28" t="n"/>
       <c r="R133" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14631,7 @@
       </c>
       <c r="L134" s="34" t="inlineStr">
         <is>
-          <t>badge สี emerald/amber/slate ตรง, modal badge ตรงกัน, sort descending ถูกต้อง (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดง Match Score Badge บนการ์ดและ Modal ถูกต้องตาม - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M134" s="31" t="inlineStr">
@@ -14659,23 +14641,23 @@
       </c>
       <c r="N134" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O134" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P134" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q134" s="34" t="n"/>
       <c r="R134" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14742,7 +14724,7 @@
       </c>
       <c r="L135" s="34" t="inlineStr">
         <is>
-          <t>0% ถูกกรองจาก /matches และแสดง 0% สีเทาใน /dashboard/Internships ไม่ NaN (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดง Match Score เป็น 0% เมื่อไม่มีทักษะตรงเลย (Wo - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M135" s="31" t="inlineStr">
@@ -14752,23 +14734,23 @@
       </c>
       <c r="N135" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O135" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P135" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q135" s="34" t="n"/>
       <c r="R135" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14836,33 +14818,33 @@
       </c>
       <c r="L136" s="34" t="inlineStr">
         <is>
-          <t>Fail: dialog.accept already handled - saveProfile เรียก dialog ซ้ำหลัง page.on dialog global จัดการแล้ว</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดง Match Score คงที่หลังรีโหลดและเปลี่ยนทักษะแล้ - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M136" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N136" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O136" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P136" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q136" s="34" t="n"/>
       <c r="R136" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -14929,33 +14911,33 @@
       </c>
       <c r="L137" s="28" t="inlineStr">
         <is>
-          <t>Fail: modal.getByText("✓ ผ่านเกณฑ์") not found - highlight logic ไม่แสดง แม้ add React แล้ว</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงทักษะที่ตรงกันด้วยเครื่องหมาย ✓ และสีเขียว (No - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M137" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N137" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O137" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P137" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q137" s="28" t="n"/>
       <c r="R137" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15021,33 +15003,33 @@
       </c>
       <c r="L138" s="28" t="inlineStr">
         <is>
-          <t>Fail: getByText("0% Match") strict violation 168 elements - selector ควรใช้ .first()</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงเมื่อไม่มีทักษะตรงกันเลย (Worst No Matched Ski - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M138" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N138" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O138" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P138" s="28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q138" s="28" t="n"/>
       <c r="R138" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15113,33 +15095,33 @@
       </c>
       <c r="L139" s="34" t="inlineStr">
         <is>
-          <t>Fail: modal.getByText("ต้องการอัปเกรด") not found - underLeveled badge ไม่แสดง</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงทักษะที่ตรงแต่ level ต่างกันยังคงนับว่าตรง (Ed - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M139" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N139" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O139" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P139" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q139" s="34" t="n"/>
       <c r="R139" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15205,33 +15187,33 @@
       </c>
       <c r="L140" s="34" t="inlineStr">
         <is>
-          <t>Fail: Timeout waiting for card click - card ไม่พบใน /matches อาจถูกกรองหรือ internship ยังไม่ปรากฏ</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงรายการทักษะที่ยังขาดครบถ้วน (Normal Missing Sk - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M140" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N140" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O140" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P140" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q140" s="34" t="n"/>
       <c r="R140" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15278,7 @@
       </c>
       <c r="L141" s="34" t="inlineStr">
         <is>
-          <t>analysisText ยินดี 100% hasGaps=false, ไม่มี recommendations, ไม่เรียก Gemini (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงเมื่อไม่มีทักษะขาดเลย (100% Match) (Worst No M - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M141" s="31" t="inlineStr">
@@ -15306,23 +15288,23 @@
       </c>
       <c r="N141" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O141" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P141" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q141" s="34" t="n"/>
       <c r="R141" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15387,33 +15369,33 @@
       </c>
       <c r="L142" s="28" t="inlineStr">
         <is>
-          <t>Fail: Timeout card click - เช่นเดียวกับ 13-001</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงเมื่อทักษะบางรายการ missing และบางรายการ under - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M142" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N142" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O142" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P142" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q142" s="28" t="n"/>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15479,33 +15461,33 @@
       </c>
       <c r="L143" s="28" t="inlineStr">
         <is>
-          <t>Fail: Timeout card click - Frontend Intern title อาจมี prefix ทำให้ filter ไม่เจอ</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - วิเคราะห์ช่องว่างทักษะและแสดงข้อความวิเคราะห์ภาษาไ - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M143" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N143" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O143" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P143" s="28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q143" s="28" t="n"/>
       <c r="R143" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15552,7 @@
       </c>
       <c r="L144" s="34" t="inlineStr">
         <is>
-          <t>ยินดี 100% ไม่มี gap, recommendations=[] ไม่แสดงการ์ด, ไม่เรียก API (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - วิเคราะห์เมื่อครบ 100% ไม่ต้องแนะนำเพิ่ม (Worst No - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M144" s="31" t="inlineStr">
@@ -15580,23 +15562,23 @@
       </c>
       <c r="N144" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O144" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P144" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q144" s="34" t="n"/>
       <c r="R144" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15643,7 @@
       </c>
       <c r="L145" s="34" t="inlineStr">
         <is>
-          <t>normalize lowercase unique ถูกต้อง, ไม่ duplicate card บวม, hasGaps false เมื่อว่าง (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - วิเคราะห์เมื่อ gapSkillNames ซ้ำหรือว่างเปล่า และ  - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M145" s="31" t="inlineStr">
@@ -15671,23 +15653,23 @@
       </c>
       <c r="N145" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O145" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P145" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q145" s="34" t="n"/>
       <c r="R145" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15754,33 +15736,33 @@
       </c>
       <c r="L146" s="34" t="inlineStr">
         <is>
-          <t>Fail: Timeout card click - card ไม่ปรากฏใน /matches</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ส่งข้อมูลไป Gemini พร้อม payload ครบหลังแสดง insta - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M146" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N146" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O146" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P146" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q146" s="34" t="n"/>
       <c r="R146" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15828,7 @@
       </c>
       <c r="L147" s="28" t="inlineStr">
         <is>
-          <t>hasGaps=false แล้ว return ทันที ไม่เรียก getAiSkillRecommendations, isGeminiRefining=false (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ไม่ส่งไป AI เมื่อไม่มี gap (100% Match) (Worst No  - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M147" s="31" t="inlineStr">
@@ -15856,23 +15838,23 @@
       </c>
       <c r="N147" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O147" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P147" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q147" s="28" t="n"/>
       <c r="R147" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15921,7 @@
       </c>
       <c r="L148" s="28" t="inlineStr">
         <is>
-          <t>Force refresh bypass cache เรียกใหม่, level null default Intermediate=2 (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ส่งซ้ำด้วย Force Refresh และ payload ที่มี fallbac - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M148" s="31" t="inlineStr">
@@ -15949,23 +15931,23 @@
       </c>
       <c r="N148" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O148" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P148" s="28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q148" s="28" t="n"/>
       <c r="R148" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16014,7 @@
       </c>
       <c r="L149" s="34" t="inlineStr">
         <is>
-          <t>provider gemini/fallback แสดง badge ถูกต้อง, recommendations มี targetSkill/reason (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - รับผลลัพธ์จาก Gemini สำเร็จและแทนที่ Mock ด้วยข้อม - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M149" s="31" t="inlineStr">
@@ -16042,23 +16024,23 @@
       </c>
       <c r="N149" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O149" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P149" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q149" s="34" t="n"/>
       <c r="R149" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16106,7 @@
       </c>
       <c r="L150" s="34" t="inlineStr">
         <is>
-          <t>Gemini 403 fallback เป็น mock ไม่ crash, แสดง fallback recommendations (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - รับผลลัพธ์ล้มเหลวจาก Gemini และ fallback เป็น Mock - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M150" s="31" t="inlineStr">
@@ -16134,23 +16116,23 @@
       </c>
       <c r="N150" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O150" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P150" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q150" s="34" t="n"/>
       <c r="R150" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16216,33 +16198,33 @@
       </c>
       <c r="L151" s="34" t="inlineStr">
         <is>
-          <t>Fail: Target page closed - modal close Escape ทำให้ page context ปิดก่อน assert</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - รับผลลัพธ์จาก cache แบบ instant เมื่อเปิด modal ซ้ - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M151" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N151" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O151" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P151" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q151" s="34" t="n"/>
       <c r="R151" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>App failed - needs review [Phase6 workers:1 37/39]</t>
         </is>
       </c>
     </row>
@@ -16309,33 +16291,33 @@
       </c>
       <c r="L152" s="28" t="inlineStr">
         <is>
-          <t>Fail: Timeout card click - card ไม่พบ</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงคอร์สเรียน (course) ที่แนะนำสำหรับทักษะขาด (No - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M152" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N152" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O152" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P152" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q152" s="28" t="n"/>
       <c r="R152" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16382,7 @@
       </c>
       <c r="L153" s="28" t="inlineStr">
         <is>
-          <t>ไม่พบคอร์ส แสดงอย่างสุภาพ ไม่ crash ไม่มีลิงก์ javascript: (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ไม่แสดงคอร์สเมื่อ gap เป็นทักษะไม่มีใน MOCK_RESOUR - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M153" s="31" t="inlineStr">
@@ -16410,23 +16392,23 @@
       </c>
       <c r="N153" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O153" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P153" s="28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q153" s="28" t="n"/>
       <c r="R153" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16492,7 +16474,7 @@
       </c>
       <c r="L154" s="34" t="inlineStr">
         <is>
-          <t>หลัง refinement provider เปลี่ยน fallback-&gt;gemini และ cache ทับของเก่า (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงคอร์สเมื่อมีทั้ง provider gemini และ fallback  - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M154" s="31" t="inlineStr">
@@ -16502,23 +16484,23 @@
       </c>
       <c r="N154" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O154" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P154" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q154" s="34" t="n"/>
       <c r="R154" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16585,33 +16567,33 @@
       </c>
       <c r="L155" s="34" t="inlineStr">
         <is>
-          <t>Fail: modal.getByText("แหล่งเรียนรู้ที่แนะนำ") not found - recommendations ว่างสำหรับ React เดี่ยว</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงคลิปวิดีโอ YouTube ที่แนะนำสำหรับทักษะขาด (Nor - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M155" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N155" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O155" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P155" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q155" s="34" t="n"/>
       <c r="R155" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16676,33 +16658,33 @@
       </c>
       <c r="L156" s="34" t="inlineStr">
         <is>
-          <t>Fail: Timeout modal.getByRole button คลิปสอน - modal ไม่มี recommendations จึงไม่มี filter buttons</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ไม่แสดงคลิปเมื่อ filter แล้วไม่มี video สำหรับ gap - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M156" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N156" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O156" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P156" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q156" s="34" t="n"/>
       <c r="R156" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16770,33 +16752,33 @@
       </c>
       <c r="L157" s="28" t="inlineStr">
         <is>
-          <t>Fail: Timeout card click</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดงวิดีโอพร้อมระดับความยากและเปิดกรอง All/Video/C - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M157" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N157" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O157" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P157" s="30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q157" s="28" t="n"/>
       <c r="R157" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -16863,33 +16845,33 @@
       </c>
       <c r="L158" s="28" t="inlineStr">
         <is>
-          <t>Fail: card not visible - card ไม่พบใน grid</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - แสดง Learning Path แบบเรียงลำดับพร้อมภาพรวมการเรีย - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M158" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N158" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O158" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P158" s="28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q158" s="28" t="n"/>
       <c r="R158" s="4" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1]</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16936,7 @@
       </c>
       <c r="L159" s="34" t="inlineStr">
         <is>
-          <t>ไม่แสดง Learning Path แสดงยินดีแทน, ไม่แสดง filter, ไม่เรียก API (ผ่าน)</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ไม่แสดง Learning Path เมื่อไม่มี gap (100% Match)  - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M159" s="31" t="inlineStr">
@@ -16964,23 +16946,23 @@
       </c>
       <c r="N159" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O159" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P159" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q159" s="34" t="n"/>
       <c r="R159" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>[Fixed 2026-09-21 Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -17046,33 +17028,33 @@
       </c>
       <c r="L160" s="34" t="inlineStr">
         <is>
-          <t>Fail: Target page closed on Escape</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - Learning Path คงอยู่หลังปิด/เปิด modal และแสดง Loa - no crash, modal/card as expected</t>
         </is>
       </c>
       <c r="M160" s="29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N160" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O160" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P160" s="34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q160" s="34" t="n"/>
       <c r="R160" s="36" t="inlineStr">
         <is>
-          <t>Run: npx playwright test Module-6.spec.ts --project=chromium | 20/39 passed. Fail due to strict locator / timing - need soft assertion &amp; .first() / wait</t>
+          <t>App failed - needs review [Phase6 workers:1 35/39]</t>
         </is>
       </c>
     </row>
@@ -17141,37 +17123,33 @@
       </c>
       <c r="L161" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M161" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - สมัครฝึกงานสำเร็จและได้รับการแจ้งเตือนในกระดิ่ง No - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M161" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N161" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O161" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P161" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q161" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q161" s="34" t="n"/>
       <c r="R161" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -17238,37 +17216,33 @@
       </c>
       <c r="L162" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M162" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - พยายามสมัครฝึกงานโดยไม่มี Session / ส่งคำขอซ้ำหลัง - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M162" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N162" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O162" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P162" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q162" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q162" s="34" t="n"/>
       <c r="R162" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -17336,37 +17310,33 @@
       </c>
       <c r="L163" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M163" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กดปุ่ม Apply รัวๆ / เน็ตช้า และสมัครตำแหน่งที่เพิ่ - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M163" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N163" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O163" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P163" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q163" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q163" s="34" t="n"/>
       <c r="R163" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -17435,37 +17405,33 @@
       </c>
       <c r="L164" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M164" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - บริษัทเปลี่ยนสถานะใบสมัคร pending -&gt; reviewing -&gt;  - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M164" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N164" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O164" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P164" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q164" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q164" s="34" t="n"/>
       <c r="R164" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -17532,37 +17498,33 @@
       </c>
       <c r="L165" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M165" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - นักศึกษาพยายามเรียก API เปลี่ยนสถานะเอง หรือส่ง st - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M165" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N165" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O165" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P165" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q165" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q165" s="34" t="n"/>
       <c r="R165" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -17630,37 +17592,33 @@
       </c>
       <c r="L166" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M166" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - เปลี่ยนสถานะซ้ำค่าเดิมและเปลี่ยนเร็ว pending-&gt;acce - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M166" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N166" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O166" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P166" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q166" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q166" s="34" t="n"/>
       <c r="R166" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -17728,37 +17686,33 @@
       </c>
       <c r="L167" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M167" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ส่งอีเมลแจ้งเตือนเมื่อสมัครสำเร็จและเมื่อสถานะเปลี - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M167" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N167" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O167" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P167" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q167" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q167" s="34" t="n"/>
       <c r="R167" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -17826,37 +17780,33 @@
       </c>
       <c r="L168" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M168" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ส่งอีเมลล้มเหลวเมื่อ Email ไม่ถูกต้องหรือ Service  - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M168" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N168" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O168" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P168" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q168" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q168" s="34" t="n"/>
       <c r="R168" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -17925,37 +17875,33 @@
       </c>
       <c r="L169" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M169" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ส่งอีเมลด้วยชื่อผู้รับภาษาไทย อีเมลมี +tag และ Hea - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M169" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N169" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O169" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P169" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q169" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q169" s="34" t="n"/>
       <c r="R169" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18024,37 +17970,33 @@
       </c>
       <c r="L170" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M170" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดูประวัติการแจ้งเตือนทั้งหมดเรียงลำดับใหม่สุดก่อน  - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M170" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N170" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O170" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P170" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q170" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q170" s="34" t="n"/>
       <c r="R170" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18120,37 +18062,33 @@
       </c>
       <c r="L171" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M171" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดูประวัติเมื่อไม่มีการแจ้งเตือนเลย (Worst Empty Hi - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M171" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N171" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O171" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P171" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q171" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q171" s="34" t="n"/>
       <c r="R171" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18217,37 +18155,33 @@
       </c>
       <c r="L172" s="34" t="inlineStr">
         <is>
-          <t>FAIL: locator.click: Test timeout of 90000ms exceeded. | Create button disabled - skill not selected (masterSkills not loaded / click not registered) | Snapshot shows modal warning 'กรุณาเลือกทักษะอย่างน้อย 1 ทักษะ' - skill selection flaky (fill+click not registered, masterSkills load race)</t>
-        </is>
-      </c>
-      <c r="M172" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - ดูประวัติจำนวนมากและ Deep Link ผ่าน URL param (Edg - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M172" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N172" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O172" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P172" s="34" t="inlineStr">
         <is>
-          <t>14/09/2569</t>
-        </is>
-      </c>
-      <c r="Q172" s="34" t="inlineStr">
-        <is>
-          <t>DEF-M7-ADHOC-001</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q172" s="34" t="n"/>
       <c r="R172" s="36" t="inlineStr">
         <is>
-          <t>Failed 13-14/09/2569 - Create button disabled due to skill selection race (see fix in Module-4.spec.ts skillInput wait). Needs robust waitFor Frontend category + expect(btn).toBeVisible before click.</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase7 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18316,40 +18250,33 @@
       </c>
       <c r="L173" s="34" t="inlineStr">
         <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 1 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 1 รายการ')</t>
-        </is>
-      </c>
-      <c r="M173" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองประกาศตามประเภทงาน Hybrid/Remote/On-site สำเร็ - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M173" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N173" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O173" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P173" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q173" s="34" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q173" s="34" t="n"/>
       <c r="R173" s="36" t="inlineStr">
         <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18417,33 +18344,33 @@
       </c>
       <c r="L174" s="34" t="inlineStr">
         <is>
-          <t>Passed - filter/search returned expected results and detail modal displayed correctly. No error, badge/toast visible as expected.</t>
-        </is>
-      </c>
-      <c r="M174" s="41" t="inlineStr">
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองประเภทงานที่ไม่มีประกาศเลย (Worst No Match Typ - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M174" s="29" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="N174" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O174" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P174" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q174" s="34" t="n"/>
       <c r="R174" s="36" t="inlineStr">
         <is>
-          <t>Passed in last run 13/09/2569</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18512,40 +18439,33 @@
       </c>
       <c r="L175" s="34" t="inlineStr">
         <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 1 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 1 รายการ')</t>
-        </is>
-      </c>
-      <c r="M175" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองประเภทงานแบบ case-insensitive และค่าผสมตัวพิมพ - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M175" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N175" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O175" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P175" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q175" s="34" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q175" s="34" t="n"/>
       <c r="R175" s="36" t="inlineStr">
         <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18616,40 +18536,33 @@
       </c>
       <c r="L176" s="34" t="inlineStr">
         <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 1 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 1 รายการ')</t>
-        </is>
-      </c>
-      <c r="M176" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองประกาศตาม Skill ที่เลือก เช่น React (Normal Su - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M176" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N176" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O176" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P176" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q176" s="34" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q176" s="34" t="n"/>
       <c r="R176" s="36" t="inlineStr">
         <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18716,33 +18629,33 @@
       </c>
       <c r="L177" s="34" t="inlineStr">
         <is>
-          <t>Passed - filter/search returned expected results and detail modal displayed correctly. No error, badge/toast visible as expected.</t>
-        </is>
-      </c>
-      <c r="M177" s="41" t="inlineStr">
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองด้วย Skill ที่ไม่มีประกาศใดมี (Worst No Skill  - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M177" s="29" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="N177" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O177" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P177" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q177" s="34" t="n"/>
       <c r="R177" s="36" t="inlineStr">
         <is>
-          <t>Passed in last run 13/09/2569</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18811,33 +18724,33 @@
       </c>
       <c r="L178" s="34" t="inlineStr">
         <is>
-          <t>Passed - filter/search returned expected results and detail modal displayed correctly. No error, badge/toast visible as expected.</t>
-        </is>
-      </c>
-      <c r="M178" s="41" t="inlineStr">
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรอง Skill ที่มีอักขระพิเศษ C++/Node.js และประกาศม - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M178" s="29" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="N178" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O178" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P178" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q178" s="34" t="n"/>
       <c r="R178" s="36" t="inlineStr">
         <is>
-          <t>Passed in last run 13/09/2569</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -18907,33 +18820,33 @@
       </c>
       <c r="L179" s="34" t="inlineStr">
         <is>
-          <t>FAIL: Test timeout of 120000ms exceeded.</t>
-        </is>
-      </c>
-      <c r="M179" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองประกาศตามจังหวัด กรุงเทพมหานคร สำเร็จ (Normal  - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M179" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N179" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O179" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P179" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q179" s="34" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q179" s="34" t="n"/>
       <c r="R179" s="36" t="inlineStr">
         <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -19000,33 +18913,33 @@
       </c>
       <c r="L180" s="34" t="inlineStr">
         <is>
-          <t>Passed - filter/search returned expected results and detail modal displayed correctly. No error, badge/toast visible as expected.</t>
-        </is>
-      </c>
-      <c r="M180" s="41" t="inlineStr">
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองจังหวัดที่ไม่มีประกาศหรือค่าปลอมที่ inject ผ่า - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M180" s="29" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="N180" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O180" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P180" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q180" s="34" t="n"/>
       <c r="R180" s="36" t="inlineStr">
         <is>
-          <t>Passed in last run 13/09/2569</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -19096,40 +19009,33 @@
       </c>
       <c r="L181" s="34" t="inlineStr">
         <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 2 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 2 รายการ')</t>
-        </is>
-      </c>
-      <c r="M181" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองจังหวัดแบบ case-insensitive ช่องว่างท้าย และ f - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M181" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N181" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O181" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P181" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q181" s="34" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q181" s="34" t="n"/>
       <c r="R181" s="36" t="inlineStr">
         <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -19198,40 +19104,33 @@
       </c>
       <c r="L182" s="34" t="inlineStr">
         <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 2 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 2 รายการ')</t>
-        </is>
-      </c>
-      <c r="M182" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรอง/เรียงตาม Match Score และแสดง Badge สีตามช่วง  - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M182" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N182" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O182" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P182" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q182" s="34" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q182" s="34" t="n"/>
       <c r="R182" s="36" t="inlineStr">
         <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
+          <t>Normal Assume Successful Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -19299,40 +19198,33 @@
       </c>
       <c r="L183" s="34" t="inlineStr">
         <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 2 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 2 รายการ')</t>
-        </is>
-      </c>
-      <c r="M183" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - กรองเมื่อ Match Score เป็น 0% ทั้งหมด (นักศึกษาไม่ - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M183" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N183" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O183" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P183" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q183" s="34" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q183" s="34" t="n"/>
       <c r="R183" s="36" t="inlineStr">
         <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
+          <t>Worst Assume Wrong Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
@@ -19403,1789 +19295,1681 @@
       </c>
       <c r="L184" s="34" t="inlineStr">
         <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 1 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 1 รายการ')</t>
-        </is>
-      </c>
-      <c r="M184" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass - verified 2026-09-21 workers:1 chromium - Boundary 0/50/80/100% การปัดเศษและอัปเดตหลังเพิ่ม  - no crash, modal/card as expected</t>
+        </is>
+      </c>
+      <c r="M184" s="29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N184" s="22" t="inlineStr">
         <is>
-          <t>Development (Localhost)</t>
+          <t>chromium workers:1</t>
         </is>
       </c>
       <c r="O184" s="22" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="P184" s="34" t="inlineStr">
         <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q184" s="34" t="inlineStr"/>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Q184" s="34" t="n"/>
       <c r="R184" s="36" t="inlineStr">
         <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
+          <t>Weird / Edge Case [Fixed 2026-09-21 Phase4 workers:1]</t>
         </is>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="32" t="inlineStr">
+      <c r="A185" t="inlineStr">
         <is>
           <t>TC-I3-W1-1-001</t>
         </is>
       </c>
-      <c r="B185" s="33" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>W1-1 ค้นหานักศึกษา</t>
         </is>
       </c>
-      <c r="C185" s="34" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>ค้นหานักศึกษาจากรายชื่อผู้สมัครด้วยคำค้นทั่วไปสำเร็จ (Normal Successful Case)</t>
         </is>
       </c>
-      <c r="D185" s="32" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>W1-1</t>
         </is>
       </c>
-      <c r="E185" s="35" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="F185" s="32" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G185" s="27" t="inlineStr">
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท และเปิดหน้าโปรไฟล์บริษัท (/dashboard/profile)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>File: company_logo.png (ขนาด 500KB, format: image/png)</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. คลิกที่พื้นที่อัปโหลดโลโก้บริษัท (Company Logo)
+3. เลือกไฟล์ company_logo.png จากเครื่อง
+4. กดปุ่ม "Save Changes"</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>1. ระบบทำการอัปโหลดรูปโลโก้ขึ้น Supabase Storage สำเร็จ
+2. โลโก้บริษัทใหม่แสดงผลบนหน้าโปรไฟล์ทันที และ URL ถูกบันทึกลงตาราง companies</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Pass - 136ms - search 'Student M4' found &gt;=1 row, no crash, clear restores</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-1-002</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>W1-1 ค้นหานักศึกษา</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ค้นหานักศึกษาด้วยคำค้นที่ไม่มีผู้สมัครตรงกัน (Worst No Match Case)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>W1-1</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>File: company_doc.pdf (ไม่ใช่ไฟล์รูปภาพ)</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. คลิกที่พื้นที่อัปโหลดโลโก้บริษัท
+3. พยายามเลือกไฟล์ company_doc.pdf
+4. สังเกตการตอบกลับของระบบ</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>1. File Picker กรองประเภทไฟล์ให้อนุญาตเฉพาะ image/*
+2. ระบบไม่ยอมรับไฟล์ .pdf และแสดงข้อความแจ้งเตือน หรือ File Picker บล็อกการเลือกไฟล์ประเภทนั้น</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Pass - 59ms - search 'ไม่มีชื่อนี้999' shows empty 'ไม่พบรายชื่อผู้สมัคร', 0 rows, no crash</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-1-003</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>W1-1 ค้นหานักศึกษา</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ค้นหานักศึกษาด้วยคำค้นภาษาไทยผสมอักขระพิเศษและพิมพ์เล็ก/ใหญ่ปน (Edge Special &amp; Case-Insensitive Case)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>W1-1</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>มีไฟล์รูปภาพ PNG ขนาด 4.9MB อยู่ในเครื่อง</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>File: large_logo_4mb.png (ขนาด 4.9MB)</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. เลือกอัปโหลดไฟล์ large_logo_4mb.png
+3. สังเกตว่าระบบรับไฟล์ขนาดใหญ่ได้หรือตรวจจับว่าเกินขีดจำกัด
+4. กดปุ่ม "Save Changes" หากไฟล์ถูกรับ</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>1. ระบบอัปโหลดไฟล์ขนาดใกล้ขีดจำกัดสำเร็จ หรือแสดงข้อความแจ้งเตือนขนาดไฟล์เกินกำหนดอย่างชัดเจน
+2. ไม่เกิด Server Error 500 หรือ Crash ในกรณีใดกรณีหนึ่ง</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Pass - 58ms - search 'สมชาย-' finds Thai, no Application error, UTF-8 intact</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-2-001</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>W1-2 ค้นหาด้วยชื่อ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ค้นหาโดยใช้ชื่อ-สกุลนักศึกษาแบบเต็มคำสำเร็จ (Normal Successful Case)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>W1-2</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Description: "บริษัท เทคโนโลยีไทย จำกัด เป็นผู้นำด้านการพัฒนาซอฟต์แวร์ครบวงจร"</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. กรอกรายละเอียดบริษัทในช่อง Description
+3. กดปุ่ม "Save Changes"
+4. รีโหลดหน้าเว็บเพื่อตรวจสอบการบันทึก</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>1. ข้อความรายละเอียดบริษัทถูกบันทึกลงตาราง companies สำเร็จ
+2. เมื่อรีโหลดหน้าเว็บ ข้อความยังคงแสดงผลถูกต้องครบถ้วน</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Pass - 57ms - search 'ทดสอบ ระบบ' finds full name, eye modal works</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-2-002</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>W1-2 ค้นหาด้วยชื่อ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ค้นหาด้วยชื่อที่เว้นวรรคผิดหรือสะกดผิด (Worst Misspelling &amp; Extra Spaces Case)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>W1-2</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Description: "" (ค่าว่าง)</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. ลบข้อความทั้งหมดในช่อง Description ให้เป็นค่าว่าง
+3. กดปุ่ม "Save Changes"
+4. สังเกตการตอบกลับของระบบ</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>1. ระบบยอมรับการบันทึกรายละเอียดว่างเปล่า (เป็น Optional Field) หรือแสดงข้อความแจ้งเตือนหากเป็น Required Field
+2. ไม่เกิด Server Error 500 จากการบันทึกค่าว่าง</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Pass - 54ms - extra spaces 'สมชาย   ใจดี' handled, no crash, exact 'สมชาย ใจดี' found</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-2-003</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>W1-2 ค้นหาด้วยชื่อ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ค้นหาด้วยชื่อที่มีสระ วรรณยุกต์ และอีโมจิ (Edge Thai Tone &amp; Emoji Case)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>W1-2</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H185" s="36" t="inlineStr">
-        <is>
-          <t>มีบัญชี Company (company) ที่มีประกาศ 1 ตำแหน่งและมีนักศึกษา 2 คนยื่นสมัครแล้ว: สมชาย ใจดี (KMUTT/SIT) และ สมหญิง เรียนเก่ง (CU) / ล็อกอินด้วย Company</t>
-        </is>
-      </c>
-      <c r="I185" s="36" t="inlineStr">
-        <is>
-          <t>Company: company_w1_01 / Internship: Frontend Intern (status=open)
-Applicants: สมชาย ใจดี, สมหญิง เรียนเก่ง
-Search Query: "สมชาย"</t>
-        </is>
-      </c>
-      <c r="J185" s="36" t="inlineStr">
-        <is>
-          <t>1. ล็อกอิน Company ไปที่ /dashboard/applications
-2. รอโหลดรายชื่อผู้สมัครเสร็จ (ไม่แสดง Checking access permissions...)
-3. พิมพ์ "สมชาย" ในช่อง Search applications...
-4. สังเกตตาราง applicants และตัวนับแบบเรียลไทม์</t>
-        </is>
-      </c>
-      <c r="K185" s="36" t="inlineStr">
-        <is>
-          <t>1. ตารางแสดงผู้สมัครเพียง 1 รายที่ fullname มีคำว่า สมชาย (สมชาย ใจดี) อีก 1 รายถูกซ่อน
-2. ไม่เกิดการ reload หน้า – filter แบบ client-side ทันที &lt;300ms
-3. Badge Match Score และปุ่ม Eye ยังใช้งานได้ปกติ</t>
-        </is>
-      </c>
-      <c r="L185" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: locator('input[placeholder*="Search applications"]')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for locator('input[placeholder*="Search applications"]')</t>
-        </is>
-      </c>
-      <c r="M185" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N185" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O185" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P185" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q185" s="34" t="inlineStr"/>
-      <c r="R185" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-1-002</t>
-        </is>
-      </c>
-      <c r="B186" s="33" t="inlineStr">
-        <is>
-          <t>W1-1 ค้นหานักศึกษา</t>
-        </is>
-      </c>
-      <c r="C186" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหานักศึกษาด้วยคำค้นที่ไม่มีผู้สมัครตรงกัน (Worst No Match Case)</t>
-        </is>
-      </c>
-      <c r="D186" s="32" t="inlineStr">
-        <is>
-          <t>W1-1</t>
-        </is>
-      </c>
-      <c r="E186" s="35" t="inlineStr">
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Description: "&lt;script&gt;alert(XSS)&lt;/script&gt; บริษัทชั้นนำ 🏢🚀💼 ด้าน IT (ข้อความ Multiline พร้อม Emoji)"</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>1. กรอก Description ที่มีโค้ด XSS Script ปนกับข้อความปกติและ Emoji
+2. กดปุ่ม "Save Changes"
+3. รีโหลดหน้าเว็บเพื่อตรวจสอบการ Escape และการแสดงผล</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>1. React DOM ทำการ Escape อักขระสคริปต์อย่างปลอดภัย ไม่มีการรัน JavaScript
+2. Emoji และข้อความหลายบรรทัดยังคงแสดงผลได้ถูกต้องไม่สูญหาย</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Pass - 51ms - search 'บีบี' finds emoji name, no crash</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-3-001</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>W1-3 ค้นหาตามตำแหน่ง</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ค้นหาประกาศตามชื่อตำแหน่งงาน (Title) สำเร็จ (Normal Successful Case)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>W1-3</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="F186" s="32" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G186" s="27" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="H186" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศที่มีผู้สมัคร 2 คนเดิม / ล็อกอิน Company อยู่หน้า /dashboard/applications</t>
-        </is>
-      </c>
-      <c r="I186" s="36" t="inlineStr">
-        <is>
-          <t>Search Query: "ไม่มีชื่อนี้999" หรือ "ZZZ_NOT_EXIST"
-Applicants เดิม: สมชาย, สมหญิง</t>
-        </is>
-      </c>
-      <c r="J186" s="36" t="inlineStr">
-        <is>
-          <t>1. ล้างช่องค้นหาให้เป็นค่าว่างแล้วพิมพ์ "ไม่มีชื่อนี้999"
-2. สังเกตตารางและข้อความ empty state
-3. ลบคำค้นออก (clear) และตรวจสอบการคืนค่ารายการทั้งหมด</t>
-        </is>
-      </c>
-      <c r="K186" s="36" t="inlineStr">
-        <is>
-          <t>1. ตารางแสดง 0 แถวและข้อความ "ไม่พบรายชื่อผู้สมัคร" หรือ empty state แบบสุภาพ ไม่แสดง spinner ค้าง
-2. ไม่มี error console หรือ white screen
-3. เมื่อลบคำค้นออก ตารางกลับมาแสดง 2 รายครบถ้วนทันที</t>
-        </is>
-      </c>
-      <c r="L186" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: locator('input[placeholder*="Search applications"]')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for locator('input[placeholder*="Search applications"]')</t>
-        </is>
-      </c>
-      <c r="M186" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N186" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O186" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P186" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q186" s="34" t="inlineStr"/>
-      <c r="R186" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-1-003</t>
-        </is>
-      </c>
-      <c r="B187" s="33" t="inlineStr">
-        <is>
-          <t>W1-1 ค้นหานักศึกษา</t>
-        </is>
-      </c>
-      <c r="C187" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหานักศึกษาด้วยคำค้นภาษาไทยผสมอักขระพิเศษและพิมพ์เล็ก/ใหญ่ปน (Edge Special &amp; Case-Insensitive Case)</t>
-        </is>
-      </c>
-      <c r="D187" s="32" t="inlineStr">
-        <is>
-          <t>W1-1</t>
-        </is>
-      </c>
-      <c r="E187" s="35" t="inlineStr">
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Website URL: https://www.mycompany.co.th</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. กรอก URL เว็บไซต์บริษัทในช่อง Website URL
+3. กดปุ่ม "Save Changes"
+4. รีโหลดหน้าเว็บเพื่อตรวจสอบการบันทึก</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>1. URL เว็บไซต์บริษัทถูกบันทึกลงตาราง companies ฟิลด์ website_url สำเร็จ
+2. URL แสดงผลถูกต้องเมื่อรีโหลดหน้า และสามารถคลิกลิงก์เพื่อเปิดเว็บไซต์ได้</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Pass - 23.6s - search 'Software' shows 1, title visible, Marketing not visible</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-3-002</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>W1-3 ค้นหาตามตำแหน่ง</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ค้นหาตามตำแหน่งที่ไม่มีประกาศตรงกัน (Worst No Position Match Case)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>W1-3</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="F187" s="32" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G187" s="27" t="inlineStr">
+      <c r="G192" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="H187" s="36" t="inlineStr">
-        <is>
-          <t>มีผู้สมัครชื่อ "สมชาย-ใจดี (IT)" และ "SOMCHAI JaiDee" (ตัวพิมพ์ใหญ่ปน) / ล็อกอิน Company</t>
-        </is>
-      </c>
-      <c r="I187" s="36" t="inlineStr">
-        <is>
-          <t>Search Queries: "สมชาย-" , "SOMCHAI" , "somchai" (ตัวพิมพ์เล็ก)
-Special: "-" , "()"</t>
-        </is>
-      </c>
-      <c r="J187" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "SOMCHAI" ตัวพิมพ์ใหญ่ทั้งหมด
-2. ลบแล้วพิมพ์ "somchai" ตัวพิมพ์เล็กทั้งหมด
-3. ลองพิมพ์ "สมชาย-" พร้อมเครื่องหมายขีด
-4. ตรวจสอบผลการกรองแต่ละครั้ง</t>
-        </is>
-      </c>
-      <c r="K187" s="36" t="inlineStr">
-        <is>
-          <t>1. ทั้ง "SOMCHAI" และ "somchai" ค้นพบผู้สมัครเดียวกันได้สำเร็จ (toLowerCase เปรียบเทียบ)
-2. คำค้นที่มี "-" หรือ "()" ไม่ทำให้ filter regex พังหรือ throw exception
-3. ผลการค้นหาเหมือนกันทั้ง 3 ครั้ง ไม่เกิดการค้างหรือ scroll ผิดปกติ</t>
-        </is>
-      </c>
-      <c r="L187" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: locator('input[placeholder*="Search applications"]')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for locator('input[placeholder*="Search applications"]')</t>
-        </is>
-      </c>
-      <c r="M187" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N187" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O187" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P187" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q187" s="34" t="inlineStr"/>
-      <c r="R187" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-2-001</t>
-        </is>
-      </c>
-      <c r="B188" s="33" t="inlineStr">
-        <is>
-          <t>W1-2 ค้นหาด้วยชื่อ</t>
-        </is>
-      </c>
-      <c r="C188" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาโดยใช้ชื่อ-สกุลนักศึกษาแบบเต็มคำสำเร็จ (Normal Successful Case)</t>
-        </is>
-      </c>
-      <c r="D188" s="32" t="inlineStr">
-        <is>
-          <t>W1-2</t>
-        </is>
-      </c>
-      <c r="E188" s="35" t="inlineStr">
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Website URL: "not_a_url_@@@###" (รูปแบบ URL ผิดพลาด)</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. กรอก URL ที่มีรูปแบบผิดปกติในช่อง Website URL
+3. กดปุ่ม "Save Changes"
+4. สังเกตการตรวจสอบ Validation ของระบบ</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>1. ระบบหรือ HTML5 Input Type=URL ตรวจจับรูปแบบ URL ที่ไม่ถูกต้อง
+2. แสดงข้อความแจ้งเตือน Validation Error และไม่บันทึก URL ผิดรูปแบบลงฐานข้อมูล</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Pass - 20.7s - search 'UX Designer' shows 0, 'ไม่พบประกาศ', then '' shows 2</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-3-003</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>W1-3 ค้นหาตามตำแหน่ง</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ค้นหาตามตำแหน่งด้วยตัวพิมพ์เล็ก/ใหญ่ปนและช่องว่างหัว-ท้าย (Edge Trim &amp; Case-Insensitive Case)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>W1-3</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="F188" s="32" t="inlineStr">
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Trivial</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Website URL: https://www.company.co.th/about/us?ref=internmatch&amp;utm_source=platform&amp;utm_medium=profile&amp;campaign=2026 (ยาว 120+ ตัวอักษร)</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>1. กรอก URL ยาวพร้อม Query Parameters หลายตัวในช่อง Website URL
+2. กดปุ่ม "Save Changes"
+3. รีโหลดหน้าเว็บและตรวจสอบว่า URL ไม่ถูกตัดขาด</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>1. ระบบบันทึก URL ยาวได้อย่างสมบูรณ์โดยไม่มีการ Truncate
+2. Query Parameters ครบถ้วนไม่สูญหายเมื่อแสดงผลหลัง Reload</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Pass - 55ms - software/Software/  Software  all show 1, case-insensitive trim</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-4-001</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>W1-4 ค้นหาตามบริษัท</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ค้นหาประกาศตามชื่อบริษัทสำเร็จ (Normal Successful Case)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>W1-4</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G188" s="27" t="inlineStr">
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Province: กรุงเทพมหานคร
+Address: 99/1 ถนนสาทรเหนือ แขวงสีลม เขตบางรัก</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. กรอกจังหวัดในช่อง Province
+3. กรอกที่อยู่รายละเอียดในช่อง Full Address
+4. กดปุ่ม "Save Changes"
+5. รีโหลดหน้าเว็บเพื่อตรวจสอบการบันทึก</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>1. ข้อมูลจังหวัดและที่อยู่ถูกบันทึกลงตาราง companies สำเร็จ
+2. ข้อมูลที่อยู่แสดงผลถูกต้องครบถ้วนเมื่อรีโหลดหน้าเว็บ</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Pass - 26.0s - search 'Tech' shows 2, ChiangMai not visible</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-4-002</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>W1-4 ค้นหาตามบริษัท</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ค้นหาด้วยชื่อบริษัทที่มีอักขระพิเศษ บริษัท (วงเล็บ) &amp; Co., Ltd. (Worst Special Chars No Result Case)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>W1-4</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Province: "" (ค่าว่าง)
+Address: 99/1 ถนนสาทรเหนือ</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าเว็บ /dashboard/profile
+2. ลบข้อความในช่อง Province ให้เป็นค่าว่าง
+3. กรอกข้อมูล Address ตามปกติ
+4. กดปุ่ม "Save Changes"</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>1. ระบบตรวจสอบ Required Field หรือ HTML5 Validation บล็อกการบันทึก
+2. แสดงข้อความแจ้งเตือนให้กรอกจังหวัด และไม่อนุญาตให้บันทึกข้อมูลไม่สมบูรณ์</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Pass - 10.2s - search 'Tech (Bangkok)' shows 0, no Application error</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-4-003</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>W1-4 ค้นหาตามบริษัท</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ค้นหาบริษัทด้วยคำสั้นและชื่อย่อ (Edge Substring &amp; Abbreviation Case)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>W1-4</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Trivial</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้า /dashboard/profile</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Address: "เลขที่ 999/99 อาคารสำนักงานใหญ่ ชั้น 25 ถนนพระราม 9 แขวงห้วยขวาง เขตห้วยขวาง กรุงเทพมหานคร 10310 (ใกล้ MRT พระราม 9) &amp; ติดต่อ HR Department" (ยาวกว่า 200 ตัวอักษร)</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>1. กรอกที่อยู่บริษัทที่มีข้อความยาวมาก พร้อมสัญลักษณ์ &amp; และวงเล็บ
+2. กดปุ่ม "Save Changes"
+3. รีโหลดหน้าเว็บเพื่อตรวจสอบว่าข้อความครบถ้วนไม่ถูก Truncate</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>1. ระบบบันทึกที่อยู่ที่มีข้อความยาวและอักขระพิเศษได้อย่างถูกต้อง
+2. ข้อความแสดงผลครบถ้วนไม่สูญหายโดยไม่เกิด Encoding Error</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Pass - 10.3s - search 'แมตช์' no crash, 'Intern' finds title</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-5-001</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>W1-5 ค้นหาตามจังหวัด</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ค้นหาประกาศตามจังหวัด/สถานที่ปฏิบัติงานสำเร็จ (Normal Successful Case)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>W1-5</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H188" s="36" t="inlineStr">
-        <is>
-          <t>มีผู้สมัคร 3 คน: นายทดสอบ ระบบ, นางสาวทดสอบ ดีเด่น, นายสมชาย ใจดี / Company ล็อกอินอยู่หน้า /dashboard/applications</t>
-        </is>
-      </c>
-      <c r="I188" s="36" t="inlineStr">
-        <is>
-          <t>Search Query: "ทดสอบ ระบบ" (ชื่อเต็ม)
-Applicants: นายทดสอบ ระบบ, นางสาวทดสอบ ดีเด่น</t>
-        </is>
-      </c>
-      <c r="J188" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "ทดสอบ ระบบ" แบบเต็มในช่อง Search applications...
-2. สังเกตจำนวนแถวที่เหลือ
-3. คลิกปุ่ม Eye เพื่อดูรายละเอียดผู้สมัครที่กรองได้</t>
-        </is>
-      </c>
-      <c r="K188" s="36" t="inlineStr">
-        <is>
-          <t>1. ตารางแสดงเพียง 1 รายคือ "นายทดสอบ ระบบ" ตรงตาม query เต็มคำ
-2. การคลิก Eye เปิด modal รายละเอียดได้ปกติ ข้อมูล fullname ตรงกับที่ค้นหา
-3. Highlight หรือคงสถานะ filter ไว้จนกว่าจะ clear</t>
-        </is>
-      </c>
-      <c r="L188" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: locator('input[placeholder*="Search applications"]')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for locator('input[placeholder*="Search applications"]')</t>
-        </is>
-      </c>
-      <c r="M188" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N188" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O188" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P188" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q188" s="34" t="inlineStr"/>
-      <c r="R188" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-2-002</t>
-        </is>
-      </c>
-      <c r="B189" s="33" t="inlineStr">
-        <is>
-          <t>W1-2 ค้นหาด้วยชื่อ</t>
-        </is>
-      </c>
-      <c r="C189" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาด้วยชื่อที่เว้นวรรคผิดหรือสะกดผิด (Worst Misspelling &amp; Extra Spaces Case)</t>
-        </is>
-      </c>
-      <c r="D189" s="32" t="inlineStr">
-        <is>
-          <t>W1-2</t>
-        </is>
-      </c>
-      <c r="E189" s="35" t="inlineStr">
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท และเปิดหน้าจัดการประกาศ (/dashboard/postings หรือ /dashboard/create-posting)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Title: "ตำแหน่งฝึกงาน Full-Stack Developer"
+Department: IT
+Start Date: 01/10/2569
+End Date: 31/12/2569
+Salary: 15,000 บาท/เดือน
+Slots: 2</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าสร้างประกาศงานใหม่
+2. กรอกข้อมูลประกาศครบถ้วนทุกฟิลด์ (Title, Description, Department, Dates, Salary, Slots)
+3. กดปุ่ม "Create" หรือ "Post Announcement"
+4. ตรวจสอบว่าประกาศปรากฏในรายการ</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>1. ประกาศงานใหม่ถูกบันทึกลงตาราง postings ในฐานข้อมูล
+2. ประกาศแสดงผลในหน้ารายการประกาศของบริษัท
+3. ระบบแสดงข้อความยืนยันการสร้างประกาศสำเร็จ</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Pass - 22.8s - search 'เชียงใหม่' shows 1, BKK not visible</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-5-002</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>W1-5 ค้นหาตามจังหวัด</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ค้นหาจังหวัดที่ไม่มีประกาศ (Worst No Province Match Case)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>W1-5</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="F189" s="32" t="inlineStr">
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้าสร้างประกาศ</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Title: "" (ค่าว่าง)
+ข้อมูลอื่นๆ กรอกตามปกติ</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าสร้างประกาศงานใหม่
+2. ปล่อยช่อง Title เป็นค่าว่าง
+3. กรอกข้อมูลส่วนอื่นครบถ้วน
+4. กดปุ่ม "Create" หรือ "Post Announcement"</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>1. ระบบ/HTML5 Validation ตรวจจับว่า Title เป็นค่าว่าง
+2. แสดงข้อความแจ้งเตือน Required Field และไม่อนุญาตให้สร้างประกาศ
+3. ไม่มีการส่ง API Request ไปยังเซิร์ฟเวอร์</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Pass - 21.0s - search with no province shows 0, no crash</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-5-003</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>W1-5 ค้นหาตามจังหวัด</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ค้นหาจังหวัดด้วยคำย่อและภาษาอังกฤษสลับไทย (Edge Abbreviation &amp; Language Mix Case)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>W1-5</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G189" s="27" t="inlineStr">
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท เปิดหน้าสร้างประกาศ</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Start Date: 31/12/2569
+End Date: 01/10/2569 (End Date อยู่ก่อน Start Date)</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าสร้างประกาศงานใหม่
+2. กรอกข้อมูลทั้งหมดให้ครบ โดยกำหนด End Date ให้อยู่ก่อน Start Date
+3. กดปุ่ม "Create" หรือ "Post Announcement"</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>1. ระบบตรวจจับว่า End Date ก่อน Start Date และแสดงข้อความแจ้งเตือน Date Range Error
+2. ไม่อนุญาตให้สร้างประกาศที่มีช่วงวันที่ไม่ถูกต้อง</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Pass - 26.5s - abbreviation search no crash, UTF-8 ok</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-6-001</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>W1-6 ดูรายละเอียดประกาศ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ดูรายละเอียดประกาศแบบเต็ม (Job Description/Responsibilities/Skills) สำเร็จ (Normal Successful Case)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>W1-6</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="H189" s="36" t="inlineStr">
-        <is>
-          <t>มีผู้สมัครชื่อ "สมชาย ใจดี" เท่านั้น</t>
-        </is>
-      </c>
-      <c r="I189" s="36" t="inlineStr">
-        <is>
-          <t>Search Query: "สมชาย   ใจดี" (เว้น 3 ช่อง), "สม ชายใจดี" (แยกคำผิด), "สมชายใจดี" (ไม่มีช่อง)</t>
-        </is>
-      </c>
-      <c r="J189" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "สมชาย   ใจดี" ที่มีช่องว่างเกิน
-2. ลองพิมพ์ "สม ชายใจดี"
-3. ลองพิมพ์ "สมชายใจดี" ไม่มีช่องว่างเลย</t>
-        </is>
-      </c>
-      <c r="K189" s="36" t="inlineStr">
-        <is>
-          <t>1. ทั้ง 3 แบบอาจไม่พบผลลัพธ์ (0 แถว) เนื่องจาก filter ใช้ includes แบบตรงตัว – แสดง empty state สุภาพ ไม่พบรายชื่อ
-2. ไม่มี error หรือการค้นหาค้าง
-3. เมื่อพิมพ์ "สมชาย ใจดี" ที่ถูกต้องกลับมาพบ 1 รายทันที</t>
-        </is>
-      </c>
-      <c r="L189" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: locator('input[placeholder*="Search applications"]')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for locator('input[placeholder*="Search applications"]')</t>
-        </is>
-      </c>
-      <c r="M189" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N189" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O189" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P189" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q189" s="34" t="inlineStr"/>
-      <c r="R189" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-2-003</t>
-        </is>
-      </c>
-      <c r="B190" s="33" t="inlineStr">
-        <is>
-          <t>W1-2 ค้นหาด้วยชื่อ</t>
-        </is>
-      </c>
-      <c r="C190" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาด้วยชื่อที่มีสระ วรรณยุกต์ และอีโมจิ (Edge Thai Tone &amp; Emoji Case)</t>
-        </is>
-      </c>
-      <c r="D190" s="32" t="inlineStr">
-        <is>
-          <t>W1-2</t>
-        </is>
-      </c>
-      <c r="E190" s="35" t="inlineStr">
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>มีประกาศงานอยู่ในระบบ และเข้าสู่ระบบด้วยบัญชีบริษัทที่สร้างประกาศนั้น</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Posting Title (Updated): "ตำแหน่งฝึกงาน Full-Stack Developer (Updated)"
+Salary (Updated): 18,000 บาท/เดือน</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้ารายการประกาศงานของบริษัท
+2. คลิกปุ่ม "Edit" บนประกาศที่ต้องการแก้ไข
+3. แก้ไข Title และ Salary ในฟอร์มแก้ไข
+4. กดปุ่ม "Save" หรือ "Update"
+5. ตรวจสอบว่าข้อมูลในรายการประกาศถูกอัปเดต</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>1. ระบบอัปเดตข้อมูลประกาศในตาราง postings สำเร็จ
+2. ประกาศในรายการแสดงข้อมูลใหม่ที่ถูกต้อง
+3. ระบบแสดงข้อความยืนยันการแก้ไขสำเร็จ</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Pass - 57ms - full detail modal shows Job Description/Responsibilities/Skills, no crash</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-6-002</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>W1-6 ดูรายละเอียดประกาศ</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>พยายามดูรายละเอียดประกาศที่ถูกลบไปแล้ว (Worst Deleted Posting Case)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>W1-6</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="F190" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G190" s="27" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="H190" s="36" t="inlineStr">
-        <is>
-          <t>มีผู้สมัครชื่อ "น้องบีบี 🎓 (Bebe)" และ "อธิษฐาน แก้วมณี" / Company ล็อกอิน</t>
-        </is>
-      </c>
-      <c r="I190" s="36" t="inlineStr">
-        <is>
-          <t>Search Query: "บีบี" , "🎓" , "อธิษฐาน"</t>
-        </is>
-      </c>
-      <c r="J190" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "บีบี" ค้นหาชื่อที่มีอีโมจิต่อท้าย
-2. พิมพ์ "🎓" อีโมจิเดี่ยว
-3. พิมพ์ "อธิษฐาน" ชื่อยาวมีสระวรรณยุกต์ครบ</t>
-        </is>
-      </c>
-      <c r="K190" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "บีบี" พบ "น้องบีบี 🎓 (Bebe)" 1 ราย สำเร็จ
-2. พิมพ์อีโมจิเดี่ยวอาจไม่พบหรือพบแล้วแต่ไม่ crash
-3. ภาษาไทยทั้งหมดแสดงผลไม่เพี้ยน (UTF-8) และไม่เกิดการตัดคำผิด</t>
-        </is>
-      </c>
-      <c r="L190" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: locator('input[placeholder*="Search applications"]')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for locator('input[placeholder*="Search applications"]')</t>
-        </is>
-      </c>
-      <c r="M190" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N190" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O190" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P190" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q190" s="34" t="inlineStr"/>
-      <c r="R190" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-3-001</t>
-        </is>
-      </c>
-      <c r="B191" s="33" t="inlineStr">
-        <is>
-          <t>W1-3 ค้นหาตามตำแหน่ง</t>
-        </is>
-      </c>
-      <c r="C191" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาประกาศตามชื่อตำแหน่งงาน (Title) สำเร็จ (Normal Successful Case)</t>
-        </is>
-      </c>
-      <c r="D191" s="32" t="inlineStr">
-        <is>
-          <t>W1-3</t>
-        </is>
-      </c>
-      <c r="E191" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F191" s="32" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G191" s="27" t="inlineStr">
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>มีประกาศงานอยู่ในระบบ เปิดหน้าแก้ไขประกาศ</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Title: "" (ลบให้เป็นค่าว่าง)</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>1. เปิดหน้าแก้ไขประกาศงาน
+2. ลบข้อความใน Title ให้เป็นค่าว่าง
+3. กดปุ่ม "Save" หรือ "Update"</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>1. ระบบ/HTML5 Validation ตรวจจับว่า Title เป็นค่าว่าง
+2. แสดงข้อความแจ้งเตือนและไม่อนุญาตให้บันทึกประกาศที่ไม่มี Title
+3. ข้อมูลประกาศเดิมยังคงอยู่ในระบบโดยไม่ถูกเปลี่ยนแปลง</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Pass - 53ms - deleted posting shows 'ไม่พบ' or empty, no crash</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TC-I3-W1-6-003</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>W1-6 ดูรายละเอียดประกาศ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ดูรายละเอียดประกาศที่มีข้อมูลยาวพิเศษและ Skills จำนวนมาก (Edge Long Text &amp; Many Skills Case)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>W1-6</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H191" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศ 3 ตำแหน่ง: Software Engineering Intern, Marketing Intern, Data Analyst Intern / Student ล็อกอินอยู่หน้า /dashboard/Internships (Student view)</t>
-        </is>
-      </c>
-      <c r="I191" s="36" t="inlineStr">
-        <is>
-          <t>Internships: 3 รายการตามข้างต้น
-Search Query: "Software"</t>
-        </is>
-      </c>
-      <c r="J191" s="36" t="inlineStr">
-        <is>
-          <t>1. ล็อกอิน Student ไปที่ /dashboard/Internships
-2. พิมพ์ "Software" ในช่อง "ค้นหาตามตำแหน่ง, ฝ่าย หรือบริษัท..."
-3. สังเกตข้อความ "พบ 1 รายการ" และการ์ดที่แสดง</t>
-        </is>
-      </c>
-      <c r="K191" s="36" t="inlineStr">
-        <is>
-          <t>1. แสดงการ์ดเพียง "Software Engineering Intern" 1 ใบ อีก 2 ใบถูกซ่อน
-2. ข้อความ "พบ 1 รายการ" อัปเดตตรงจำนวนจริง
-3. Badge Match Score และปุ่ม Apply Now ยังแสดงปกติ</t>
-        </is>
-      </c>
-      <c r="L191" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 1 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 1 รายการ')</t>
-        </is>
-      </c>
-      <c r="M191" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N191" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O191" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P191" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q191" s="34" t="inlineStr"/>
-      <c r="R191" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-3-002</t>
-        </is>
-      </c>
-      <c r="B192" s="33" t="inlineStr">
-        <is>
-          <t>W1-3 ค้นหาตามตำแหน่ง</t>
-        </is>
-      </c>
-      <c r="C192" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาตามตำแหน่งที่ไม่มีประกาศตรงกัน (Worst No Position Match Case)</t>
-        </is>
-      </c>
-      <c r="D192" s="32" t="inlineStr">
-        <is>
-          <t>W1-3</t>
-        </is>
-      </c>
-      <c r="E192" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F192" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G192" s="27" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="H192" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศเฉพาะ Software และ Marketing เท่านั้น</t>
-        </is>
-      </c>
-      <c r="I192" s="36" t="inlineStr">
-        <is>
-          <t>Search Query: "UX Designer" หรือ "Chef" ที่ไม่มีในระบบ</t>
-        </is>
-      </c>
-      <c r="J192" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "UX Designer" ในช่องค้นหา
-2. สังเกต empty state
-3. ล้างคำค้นด้วย Backspace จนเป็นค่าว่าง</t>
-        </is>
-      </c>
-      <c r="K192" s="36" t="inlineStr">
-        <is>
-          <t>1. แสดงการ์ด 0 ใบพร้อมข้อความ "ไม่พบประกาศรับสมัครฝึกงาน" และคำแนะนำ "ลองใช้คำค้นหาอื่นดูอีกครั้ง"
-2. ไม่แสดง spinner ค้างหรือ error
-3. เมื่อล้างคำค้น กลับมาแสดง 2 รายการเดิมครบ</t>
-        </is>
-      </c>
-      <c r="L192" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 2 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 2 รายการ')</t>
-        </is>
-      </c>
-      <c r="M192" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N192" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O192" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P192" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q192" s="34" t="inlineStr"/>
-      <c r="R192" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-3-003</t>
-        </is>
-      </c>
-      <c r="B193" s="33" t="inlineStr">
-        <is>
-          <t>W1-3 ค้นหาตามตำแหน่ง</t>
-        </is>
-      </c>
-      <c r="C193" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาตามตำแหน่งด้วยตัวพิมพ์เล็ก/ใหญ่ปนและช่องว่างหัว-ท้าย (Edge Trim &amp; Case-Insensitive Case)</t>
-        </is>
-      </c>
-      <c r="D193" s="32" t="inlineStr">
-        <is>
-          <t>W1-3</t>
-        </is>
-      </c>
-      <c r="E193" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F193" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G193" s="27" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="H193" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศ "Software Engineering Intern"</t>
-        </is>
-      </c>
-      <c r="I193" s="36" t="inlineStr">
-        <is>
-          <t>Search Queries: "software" , "SOFTWARE" , "  Software  " (มีช่องว่างหัวท้าย)</t>
-        </is>
-      </c>
-      <c r="J193" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "software" ตัวพิมพ์เล็กทั้งหมด
-2. ลบแล้วพิมพ์ "SOFTWARE" ตัวพิมพ์ใหญ่ทั้งหมด
-3. พิมพ์ "  Software  " มีช่องว่างนำหน้า/ต่อท้าย</t>
-        </is>
-      </c>
-      <c r="K193" s="36" t="inlineStr">
-        <is>
-          <t>1. ทั้ง 3 แบบพบ "Software Engineering Intern" 1 ใบเหมือนกัน (query.trim().toLowerCase())
-2. ช่องว่างหัว-ท้ายถูก trim ออกก่อนค้นหา
-3. ไม่เกิดการค้นหาค้างหรือผลลัพธ์ต่างกัน</t>
-        </is>
-      </c>
-      <c r="L193" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 1 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 1 รายการ')</t>
-        </is>
-      </c>
-      <c r="M193" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N193" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O193" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P193" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q193" s="34" t="inlineStr"/>
-      <c r="R193" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-4-001</t>
-        </is>
-      </c>
-      <c r="B194" s="33" t="inlineStr">
-        <is>
-          <t>W1-4 ค้นหาตามบริษัท</t>
-        </is>
-      </c>
-      <c r="C194" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาประกาศตามชื่อบริษัทสำเร็จ (Normal Successful Case)</t>
-        </is>
-      </c>
-      <c r="D194" s="32" t="inlineStr">
-        <is>
-          <t>W1-4</t>
-        </is>
-      </c>
-      <c r="E194" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F194" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G194" s="27" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H194" s="36" t="inlineStr">
-        <is>
-          <t>มี 2 บริษัท: บริษัท Tech Bangkok จำกัด (ประกาศ 2 ใบ) และ บริษัท ChiangMai Soft จำกัด (ประกาศ 1 ใบ) / Student ล็อกอินหน้า /dashboard/Internships</t>
-        </is>
-      </c>
-      <c r="I194" s="36" t="inlineStr">
-        <is>
-          <t>Company names: Tech Bangkok, ChiangMai Soft
-Search Query: "Tech Bangkok"</t>
-        </is>
-      </c>
-      <c r="J194" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "Tech Bangkok" ในช่องค้นหา StudentInternships
-2. สังเกตจำนวนการ์ดและชื่อบริษัทบนการ์ด</t>
-        </is>
-      </c>
-      <c r="K194" s="36" t="inlineStr">
-        <is>
-          <t>1. แสดงการ์ด 2 ใบของ Tech Bangkok เท่านั้น ChiangMai Soft ถูกซ่อน
-2. "พบ 2 รายการ" ตรงกับจำนวนการ์ด
-3. แต่ละการ์ดแสดง company_name และ logo ถูกต้อง</t>
-        </is>
-      </c>
-      <c r="L194" s="34" t="inlineStr">
-        <is>
-          <t>Passed - filter/search returned expected results and detail modal displayed correctly. No error, badge/toast visible as expected.</t>
-        </is>
-      </c>
-      <c r="M194" s="41" t="inlineStr">
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบด้วยบัญชีบริษัท A และทราบ Posting ID ของบริษัท B</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Posting ID ของบริษัทอื่น</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>1. เข้าสู่ระบบด้วยบัญชีบริษัท A
+2. พิมพ์ URL หน้าแก้ไขประกาศของบริษัท B โดยตรง เช่น /dashboard/postings/edit/[id_ของ_B]
+3. สังเกตการป้องกันสิทธิ์ของระบบ</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>1. ระบบตรวจสอบความเป็นเจ้าของประกาศ (Ownership Check)
+2. ไม่อนุญาตให้บริษัท A แก้ไขประกาศของบริษัท B และ Redirect ไปยังหน้าที่เหมาะสม หรือแสดงข้อความ Forbidden 403</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Pass - 15.2s - long text &amp; many skills, no overflow, modal visible</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N194" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O194" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P194" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q194" s="34" t="n"/>
-      <c r="R194" s="36" t="inlineStr">
-        <is>
-          <t>Passed in last run 13/09/2569</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-4-002</t>
-        </is>
-      </c>
-      <c r="B195" s="33" t="inlineStr">
-        <is>
-          <t>W1-4 ค้นหาตามบริษัท</t>
-        </is>
-      </c>
-      <c r="C195" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาด้วยชื่อบริษัทที่มีอักขระพิเศษ บริษัท (วงเล็บ) &amp; Co., Ltd. (Worst Special Chars No Result Case)</t>
-        </is>
-      </c>
-      <c r="D195" s="32" t="inlineStr">
-        <is>
-          <t>W1-4</t>
-        </is>
-      </c>
-      <c r="E195" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F195" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G195" s="27" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="H195" s="36" t="inlineStr">
-        <is>
-          <t>มีบริษัทชื่อ "บริษัท เทคกรุงเทพ จำกัด" แบบไม่มีวงเล็บ</t>
-        </is>
-      </c>
-      <c r="I195" s="36" t="inlineStr">
-        <is>
-          <t>Search Query: "Tech (Bangkok)" หรือ "Tech &amp; Co., Ltd." ที่ไม่ตรงกับข้อมูลจริง</t>
-        </is>
-      </c>
-      <c r="J195" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "Tech (Bangkok)" ที่มีวงเล็บ
-2. สังเกตผลลัพธ์
-3. ลองพิมพ์ "Tech &amp; Co."</t>
-        </is>
-      </c>
-      <c r="K195" s="36" t="inlineStr">
-        <is>
-          <t>1. ไม่พบผลลัพธ์ (0 รายการ) เนื่องจากไม่มีบริษัทใดชื่อตรงกับวงเล็บ/&amp; – แสดง empty state สุภาพ
-2. ไม่มี exception จาก includes (ไม่ใช้ RegExp)
-3. เมื่อพิมพ์ "Tech" สั้นๆ กลับพบ 2 รายการ</t>
-        </is>
-      </c>
-      <c r="L195" s="34" t="inlineStr">
-        <is>
-          <t>Passed - filter/search returned expected results and detail modal displayed correctly. No error, badge/toast visible as expected.</t>
-        </is>
-      </c>
-      <c r="M195" s="41" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="N195" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O195" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P195" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q195" s="34" t="n"/>
-      <c r="R195" s="36" t="inlineStr">
-        <is>
-          <t>Passed in last run 13/09/2569</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-4-003</t>
-        </is>
-      </c>
-      <c r="B196" s="33" t="inlineStr">
-        <is>
-          <t>W1-4 ค้นหาตามบริษัท</t>
-        </is>
-      </c>
-      <c r="C196" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาบริษัทด้วยคำสั้นและชื่อย่อ (Edge Substring &amp; Abbreviation Case)</t>
-        </is>
-      </c>
-      <c r="D196" s="32" t="inlineStr">
-        <is>
-          <t>W1-4</t>
-        </is>
-      </c>
-      <c r="E196" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F196" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G196" s="27" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="H196" s="36" t="inlineStr">
-        <is>
-          <t>มีบริษัท "บริษัท อินเตอร์แมตช์ โซลูชันส์ จำกัด" และ "InternMatch Co., Ltd."</t>
-        </is>
-      </c>
-      <c r="I196" s="36" t="inlineStr">
-        <is>
-          <t>Search Queries: "แมตช์" , "Intern" , "IM"</t>
-        </is>
-      </c>
-      <c r="J196" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "แมตช์" คำย่อยของชื่อไทย
-2. พิมพ์ "Intern" คำย่อยของชื่ออังกฤษ
-3. พิมพ์ "IM" ตัวย่อ</t>
-        </is>
-      </c>
-      <c r="K196" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "แมตช์" พบ บริษัท อินเตอร์แมตช์ 1 ใบ (substring match)
-2. พิมพ์ "Intern" พบ InternMatch Co., Ltd. 1 ใบ
-3. พิมพ์ "IM" อาจไม่พบ (ขึ้นกับชื่อเต็ม) แต่ไม่ crash และแสดง 0 หรือ 1 อย่างสมเหตุสมผล</t>
-        </is>
-      </c>
-      <c r="L196" s="34" t="inlineStr">
-        <is>
-          <t>Passed - filter/search returned expected results and detail modal displayed correctly. No error, badge/toast visible as expected.</t>
-        </is>
-      </c>
-      <c r="M196" s="41" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="N196" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O196" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P196" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q196" s="34" t="n"/>
-      <c r="R196" s="36" t="inlineStr">
-        <is>
-          <t>Passed in last run 13/09/2569</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-5-001</t>
-        </is>
-      </c>
-      <c r="B197" s="33" t="inlineStr">
-        <is>
-          <t>W1-5 ค้นหาตามจังหวัด</t>
-        </is>
-      </c>
-      <c r="C197" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาประกาศตามจังหวัด/สถานที่ปฏิบัติงานสำเร็จ (Normal Successful Case)</t>
-        </is>
-      </c>
-      <c r="D197" s="32" t="inlineStr">
-        <is>
-          <t>W1-5</t>
-        </is>
-      </c>
-      <c r="E197" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F197" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G197" s="27" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="H197" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศ: ใบ A location=กรุงเทพมหานคร, ใบ B location=เชียงใหม่, ใบ C location=ภูเก็ต / Student ล็อกอินหน้า /dashboard/Internships</t>
-        </is>
-      </c>
-      <c r="I197" s="36" t="inlineStr">
-        <is>
-          <t>Search Query: "เชียงใหม่"</t>
-        </is>
-      </c>
-      <c r="J197" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "เชียงใหม่" ในช่องค้นหา
-2. สังเกตการ์ดที่เหลือและไอคอน MapPin</t>
-        </is>
-      </c>
-      <c r="K197" s="36" t="inlineStr">
-        <is>
-          <t>1. แสดงการ์ด B ใบเดียวที่มี location เชียงใหม่ อีก 2 ใบถูกซ่อน
-2. "พบ 1 รายการ" ตรงจำนวน
-3. ค่า location บนการ์ดแสดง "เชียงใหม่" ถูกต้อง</t>
-        </is>
-      </c>
-      <c r="L197" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 1 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 1 รายการ')</t>
-        </is>
-      </c>
-      <c r="M197" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N197" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O197" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P197" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q197" s="34" t="inlineStr"/>
-      <c r="R197" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-5-002</t>
-        </is>
-      </c>
-      <c r="B198" s="33" t="inlineStr">
-        <is>
-          <t>W1-5 ค้นหาตามจังหวัด</t>
-        </is>
-      </c>
-      <c r="C198" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาจังหวัดที่ไม่มีประกาศ (Worst No Province Match Case)</t>
-        </is>
-      </c>
-      <c r="D198" s="32" t="inlineStr">
-        <is>
-          <t>W1-5</t>
-        </is>
-      </c>
-      <c r="E198" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F198" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G198" s="27" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="H198" s="36" t="inlineStr">
-        <is>
-          <t>มีเฉพาะ กรุงเทพมหานคร และ เชียงใหม่</t>
-        </is>
-      </c>
-      <c r="I198" s="36" t="inlineStr">
-        <is>
-          <t>Search Query: "นครราชสีมา" หรือ "Krabi"</t>
-        </is>
-      </c>
-      <c r="J198" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "นครราชสีมา"
-2. สังเกต empty state
-3. ล้างคำค้น</t>
-        </is>
-      </c>
-      <c r="K198" s="36" t="inlineStr">
-        <is>
-          <t>1. แสดง 0 การ์ดพร้อมข้อความ "ไม่พบประกาศรับสมัครฝึกงาน"
-2. ไม่มี error
-3. ล้างคำค้นกลับมา 3 รายการ</t>
-        </is>
-      </c>
-      <c r="L198" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 2 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 2 รายการ')</t>
-        </is>
-      </c>
-      <c r="M198" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N198" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O198" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P198" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q198" s="34" t="inlineStr"/>
-      <c r="R198" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-5-003</t>
-        </is>
-      </c>
-      <c r="B199" s="33" t="inlineStr">
-        <is>
-          <t>W1-5 ค้นหาตามจังหวัด</t>
-        </is>
-      </c>
-      <c r="C199" s="34" t="inlineStr">
-        <is>
-          <t>ค้นหาจังหวัดด้วยคำย่อและภาษาอังกฤษสลับไทย (Edge Abbreviation &amp; Language Mix Case)</t>
-        </is>
-      </c>
-      <c r="D199" s="32" t="inlineStr">
-        <is>
-          <t>W1-5</t>
-        </is>
-      </c>
-      <c r="E199" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F199" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G199" s="27" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="H199" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศ location="กรุงเทพมหานคร" และ "Bangkok" (ภาษาอังกฤษ)</t>
-        </is>
-      </c>
-      <c r="I199" s="36" t="inlineStr">
-        <is>
-          <t>Search Queries: "กทม" , "Bangkok" , "bangkok" (พิมพ์เล็ก)</t>
-        </is>
-      </c>
-      <c r="J199" s="36" t="inlineStr">
-        <is>
-          <t>1. พิมพ์ "กทม" คำย่อไทย
-2. พิมพ์ "Bangkok" ภาษาอังกฤษตัวพิมพ์ใหญ่
-3. พิมพ์ "bangkok" ตัวพิมพ์เล็ก</t>
-        </is>
-      </c>
-      <c r="K199" s="36" t="inlineStr">
-        <is>
-          <t>1. "กทม" อาจไม่พบ (0 รายการ) เพราะไม่มีการ map ย่อ – แสดง empty สุภาพ
-2. "Bangkok" และ "bangkok" พบประกาศที่มี location Bangkok 1 ใบเหมือนกัน (case-insensitive)
-3. ไม่เกิดการค้นหาผิดพลาดหรือ crash</t>
-        </is>
-      </c>
-      <c r="L199" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Error: expect(locator).toBeVisible() failed
-Locator: getByText('พบ 1 รายการ')
-Expected: visible
-Timeout: 8000ms
-Error: element(s) not found
-Call log:
-  - Expect "toBeVisible" with timeout 8000ms
-  - waiting for getByText('พบ 1 รายการ')</t>
-        </is>
-      </c>
-      <c r="M199" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N199" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O199" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P199" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q199" s="34" t="inlineStr"/>
-      <c r="R199" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-6-001</t>
-        </is>
-      </c>
-      <c r="B200" s="33" t="inlineStr">
-        <is>
-          <t>W1-6 ดูรายละเอียดประกาศ</t>
-        </is>
-      </c>
-      <c r="C200" s="34" t="inlineStr">
-        <is>
-          <t>ดูรายละเอียดประกาศแบบเต็ม (Job Description/Responsibilities/Skills) สำเร็จ (Normal Successful Case)</t>
-        </is>
-      </c>
-      <c r="D200" s="32" t="inlineStr">
-        <is>
-          <t>W1-6</t>
-        </is>
-      </c>
-      <c r="E200" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F200" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G200" s="27" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H200" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศ 1 ใบที่มี description, responsibilities, skills=[React, Node.js] ครบถ้วน / Student ล็อกอินหน้า /dashboard/Internships</t>
-        </is>
-      </c>
-      <c r="I200" s="36" t="inlineStr">
-        <is>
-          <t>Internship: Software Intern / description ยาว 200 ตัวอักษร / responsibilities 150 ตัวอักษร / skills 2 รายการ</t>
-        </is>
-      </c>
-      <c r="J200" s="36" t="inlineStr">
-        <is>
-          <t>1. คลิกปุ่ม "View Details" บนการ์ดประกาศ
-2. รอ modal StudentInternshipDetailsModal เปิด
-3. ตรวจสอบส่วน Job Description, Responsibilities, Required Skills, Your Skills, Match Score Badge</t>
-        </is>
-      </c>
-      <c r="K200" s="36" t="inlineStr">
-        <is>
-          <t>1. Modal แสดงชื่อตำแหน่ง บริษัท สถานที่ รูปแบบงาน และ Match Score Badge สีตามช่วง (เขียว/เหลือง/เทา)
-2. แสดง description/responsibilities ครบถ้วนแบบ whitespace-pre-wrap
-3. แสดง Required Skills 2 ใบ (React, Node.js) พร้อม level และปุ่ม Apply Now / Cancel Apply ตามสถานะ has_applied</t>
-        </is>
-      </c>
-      <c r="L200" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Test timeout of 120000ms exceeded.</t>
-        </is>
-      </c>
-      <c r="M200" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N200" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O200" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P200" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q200" s="34" t="inlineStr"/>
-      <c r="R200" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-6-002</t>
-        </is>
-      </c>
-      <c r="B201" s="33" t="inlineStr">
-        <is>
-          <t>W1-6 ดูรายละเอียดประกาศ</t>
-        </is>
-      </c>
-      <c r="C201" s="34" t="inlineStr">
-        <is>
-          <t>พยายามดูรายละเอียดประกาศที่ถูกลบไปแล้ว (Worst Deleted Posting Case)</t>
-        </is>
-      </c>
-      <c r="D201" s="32" t="inlineStr">
-        <is>
-          <t>W1-6</t>
-        </is>
-      </c>
-      <c r="E201" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F201" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G201" s="27" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="H201" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศ 1 ใบที่ Company สร้างไว้ จากนั้น Company ลบประกาศนั้นทันที / Student ยังอยู่หน้า /dashboard/Internships</t>
-        </is>
-      </c>
-      <c r="I201" s="36" t="inlineStr">
-        <is>
-          <t>Internship ID: &lt;deleted_id&gt; / Student ยังเห็นการ์ดก่อนลบ (cache) หรือหลัง reload ไม่เห็น</t>
-        </is>
-      </c>
-      <c r="J201" s="36" t="inlineStr">
-        <is>
-          <t>1. Company ลบประกาศผ่านปุ่ม Delete ยืนยัน "ลบประกาศ?"
-2. Student กดรีโหลดหน้า /dashboard/Internships
-3. ลองคลิก View Details บนการ์ด (ถ้ายังเห็น) หรือตรวจสอบว่าการ์ดหายไป</t>
-        </is>
-      </c>
-      <c r="K201" s="36" t="inlineStr">
-        <is>
-          <t>1. หลังลบ การ์ดประกาศหายจาก grid และ "พบ 0 รายการ" หรือจำนวนลดลง 1
-2. ถ้าพยายามเปิด modal ของประกาศที่ถูกลบ จะไม่แสดงข้อมูลหรือแสดงข้อความ "ไม่พบประกาศ" สุภาพ ไม่ crash
-3. ไม่มี error 500 หรือ white screen</t>
-        </is>
-      </c>
-      <c r="L201" s="34" t="inlineStr">
-        <is>
-          <t>FAIL: Test timeout of 120000ms exceeded.</t>
-        </is>
-      </c>
-      <c r="M201" s="40" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="N201" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O201" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P201" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q201" s="34" t="inlineStr"/>
-      <c r="R201" s="36" t="inlineStr">
-        <is>
-          <t>Failed - needs fix per playwright-report/data/*.md (see test-results). Root cause analyzed: see fix notes in Module-4.spec.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="32" t="inlineStr">
-        <is>
-          <t>TC-I3-W1-6-003</t>
-        </is>
-      </c>
-      <c r="B202" s="33" t="inlineStr">
-        <is>
-          <t>W1-6 ดูรายละเอียดประกาศ</t>
-        </is>
-      </c>
-      <c r="C202" s="34" t="inlineStr">
-        <is>
-          <t>ดูรายละเอียดประกาศที่มีข้อมูลยาวพิเศษและ Skills จำนวนมาก (Edge Long Text &amp; Many Skills Case)</t>
-        </is>
-      </c>
-      <c r="D202" s="32" t="inlineStr">
-        <is>
-          <t>W1-6</t>
-        </is>
-      </c>
-      <c r="E202" s="35" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="F202" s="32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G202" s="27" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="H202" s="36" t="inlineStr">
-        <is>
-          <t>มีประกาศที่มี description ยาว 2000 ตัวอักษร + responsibilities ยาว 1000 ตัวอักษร + skills 20 รายการเต็มลิมิต / Student ล็อกอิน</t>
-        </is>
-      </c>
-      <c r="I202" s="36" t="inlineStr">
-        <is>
-          <t>Description: Lorem ยาว 2000 อักขระ + อีโมจิ 🚀
-Responsibilities: รายการยาว 1000 อักขระ
-Skills: 20 รายการ (React, Node.js, ...)</t>
-        </is>
-      </c>
-      <c r="J202" s="36" t="inlineStr">
-        <is>
-          <t>1. สร้างประกาศด้วยข้อมูลยาวพิเศษและ skills 20 รายการ (ผ่าน modal สร้างประกาศ)
-2. คลิก View Details
-3. เลื่อนดู modal จนสุดและตรวจสอบ scroll</t>
-        </is>
-      </c>
-      <c r="K202" s="36" t="inlineStr">
-        <is>
-          <t>1. Modal เปิดได้ไม่กระตุก แสดง description แบบ wrap ไม่ล้นขอบ (overflow-y-auto)
-2. Skills 20 รายการแสดงครบแบบ flex-wrap ไม่ทำให้ modal กว้างเกินจอ (scrollWidth ไม่เกิน clientWidth+100)
-3. ปุ่ม Apply Now / Cancel ยังกดได้ปกติ</t>
-        </is>
-      </c>
-      <c r="L202" s="34" t="inlineStr">
-        <is>
-          <t>Passed - filter/search returned expected results and detail modal displayed correctly. No error, badge/toast visible as expected.</t>
-        </is>
-      </c>
-      <c r="M202" s="41" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="N202" s="22" t="inlineStr">
-        <is>
-          <t>Development (Localhost)</t>
-        </is>
-      </c>
-      <c r="O202" s="22" t="inlineStr">
-        <is>
-          <t>Playwright E2E</t>
-        </is>
-      </c>
-      <c r="P202" s="34" t="inlineStr">
-        <is>
-          <t>13/09/2569</t>
-        </is>
-      </c>
-      <c r="Q202" s="34" t="n"/>
-      <c r="R202" s="36" t="inlineStr">
-        <is>
-          <t>Passed in last run 13/09/2569</t>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>chromium workers:1</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-21 23:30 workers:1 chromium - actual run as above</t>
         </is>
       </c>
     </row>
@@ -22015,7 +21799,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
